--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF33"/>
+  <dimension ref="A1:AG34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,150 +436,155 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>gap_days</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>personnel_total</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>personnel_daily</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>tanks_total</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tanks_daily</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>afv_total</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>afv_daily</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>artillery_total</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>artillery_daily</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>mlrs_total</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>mlrs_daily</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>airdef_total</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>airdef_daily</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>planes_total</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>planes_daily</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>helicopters_total</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>helicopters_daily</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>uav_total</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>uav_daily</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>missiles_total</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>missiles_daily</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>ships_total</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>ships_daily</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>submarines_total</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>submarines_daily</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>vehicles_total</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>vehicles_daily</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>special_total</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>special_daily</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>robots_total</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>robots_daily</t>
         </is>
@@ -595,93 +600,96 @@
         <v>1528</v>
       </c>
       <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>1331710</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>11903</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>24496</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>41044</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1757</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>1357</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>435</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>352</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
         <v>265284</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>4579</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
       <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>33</v>
       </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>93009</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
       <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
         <v>4150</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -695,93 +703,96 @@
         <v>1529</v>
       </c>
       <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>1332950</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>1240</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>11906</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>3</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>24500</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>41117</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>73</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1763</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>6</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1357</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>435</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>352</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
         <v>267589</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>2305</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>4579</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>33</v>
       </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
         <v>93274</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>265</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>4151</v>
       </c>
-      <c r="AD3" t="n">
-        <v>1</v>
-      </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -795,93 +806,96 @@
         <v>1530</v>
       </c>
       <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>1334030</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1080</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>11908</v>
       </c>
-      <c r="F4" t="n">
-        <v>2</v>
-      </c>
       <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
         <v>24503</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>41193</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>76</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>1765</v>
       </c>
-      <c r="L4" t="n">
-        <v>2</v>
-      </c>
       <c r="M4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" t="n">
         <v>1357</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>435</v>
       </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
       <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
         <v>352</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>269813</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>2224</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>4579</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
         <v>33</v>
       </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
       <c r="Y4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
         <v>93556</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>282</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>4151</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
       <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
         <v>1306</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -895,93 +909,96 @@
         <v>1531</v>
       </c>
       <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>1335150</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1120</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>11914</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>6</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>24507</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>41306</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>113</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1767</v>
       </c>
-      <c r="L5" t="n">
-        <v>2</v>
-      </c>
       <c r="M5" t="n">
+        <v>2</v>
+      </c>
+      <c r="N5" t="n">
         <v>1357</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>435</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>352</v>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
       <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>272062</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>2249</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>4584</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>5</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>33</v>
       </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>93824</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>268</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>4168</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>17</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>1317</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>11</v>
       </c>
     </row>
@@ -995,93 +1012,96 @@
         <v>1532</v>
       </c>
       <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>1336120</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>970</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>11917</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>24510</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>41386</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>80</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>1770</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>1361</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>4</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>435</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>352</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
         <v>274030</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1968</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>4584</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
         <v>33</v>
       </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
       <c r="Y6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
         <v>94030</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AC6" t="n">
         <v>206</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
         <v>4170</v>
       </c>
-      <c r="AD6" t="n">
-        <v>2</v>
-      </c>
       <c r="AE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1320</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AG6" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1095,93 +1115,96 @@
         <v>1533</v>
       </c>
       <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>1337170</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>1050</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>11918</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>24515</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>41478</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>92</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>1775</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>5</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1363</v>
       </c>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
       <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
         <v>435</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>352</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
       <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
         <v>276061</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>2031</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>4585</v>
       </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
       <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
         <v>33</v>
       </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
         <v>94312</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AC7" t="n">
         <v>282</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
         <v>4170</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
       <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
         <v>1332</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AG7" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1195,93 +1218,96 @@
         <v>1534</v>
       </c>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>1338060</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>890</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>11918</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>24521</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>41539</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>61</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1776</v>
       </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
       <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
         <v>1365</v>
       </c>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
       <c r="O8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P8" t="n">
         <v>435</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>352</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>277912</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>1851</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>4585</v>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
       <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
         <v>33</v>
       </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
       <c r="Y8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
         <v>94545</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
         <v>233</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
         <v>4172</v>
       </c>
-      <c r="AD8" t="n">
-        <v>2</v>
-      </c>
       <c r="AE8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF8" t="n">
         <v>1336</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1295,93 +1321,96 @@
         <v>1535</v>
       </c>
       <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>1339190</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>1130</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>11919</v>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>24538</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>17</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>41630</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>91</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>1778</v>
       </c>
-      <c r="L9" t="n">
-        <v>2</v>
-      </c>
       <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
         <v>1370</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>5</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>435</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>352</v>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
       <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>279729</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>1817</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>4585</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
         <v>33</v>
       </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
         <v>94879</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
         <v>334</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AD9" t="n">
         <v>4173</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1</v>
-      </c>
       <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1344</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AG9" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1395,93 +1424,96 @@
         <v>1536</v>
       </c>
       <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
         <v>1340270</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>1080</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>11920</v>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>24541</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>41712</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>82</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>1780</v>
       </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
       <c r="M10" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" t="n">
         <v>1371</v>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
       <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
         <v>435</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>352</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
         <v>281208</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>1479</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>4585</v>
       </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
       <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
         <v>33</v>
       </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
         <v>95252</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AC10" t="n">
         <v>373</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AD10" t="n">
         <v>4173</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
       <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1351</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AG10" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1495,93 +1527,96 @@
         <v>1537</v>
       </c>
       <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
         <v>1341110</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>840</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>11920</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
         <v>24544</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>41787</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>75</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1782</v>
       </c>
-      <c r="L11" t="n">
-        <v>2</v>
-      </c>
       <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
         <v>1373</v>
       </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
       <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="n">
         <v>435</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>352</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
       <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
         <v>282697</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>1489</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>4585</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
       <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
         <v>33</v>
       </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
         <v>95479</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
         <v>227</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AD11" t="n">
         <v>4176</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AE11" t="n">
         <v>3</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AF11" t="n">
         <v>1362</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1595,93 +1630,96 @@
         <v>1538</v>
       </c>
       <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
         <v>1342030</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>920</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>11924</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>4</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>24551</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>7</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>41863</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>76</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>1783</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
       <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="n">
         <v>1373</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>435</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>352</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
         <v>284254</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>1557</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>4585</v>
       </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
         <v>33</v>
       </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
       <c r="Y12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
         <v>95710</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AC12" t="n">
         <v>231</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AD12" t="n">
         <v>4178</v>
       </c>
-      <c r="AD12" t="n">
-        <v>2</v>
-      </c>
       <c r="AE12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF12" t="n">
         <v>1371</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AG12" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1695,93 +1733,96 @@
         <v>1539</v>
       </c>
       <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
         <v>1343050</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1020</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>11926</v>
       </c>
-      <c r="F13" t="n">
-        <v>2</v>
-      </c>
       <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
         <v>24553</v>
       </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
       <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
         <v>41935</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>72</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>1785</v>
       </c>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
       <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="n">
         <v>1373</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>435</v>
       </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>352</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>285506</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>1252</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>4585</v>
       </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
         <v>33</v>
       </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
         <v>95855</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
         <v>145</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
         <v>4179</v>
       </c>
-      <c r="AD13" t="n">
-        <v>1</v>
-      </c>
       <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1373</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1795,93 +1836,96 @@
         <v>1540</v>
       </c>
       <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
         <v>1344180</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1130</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>11928</v>
       </c>
-      <c r="F14" t="n">
-        <v>2</v>
-      </c>
       <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
         <v>24554</v>
       </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
       <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
         <v>41985</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>50</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1786</v>
       </c>
-      <c r="L14" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="n">
         <v>1376</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>3</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>435</v>
       </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
       <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>352</v>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
         <v>287359</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>1853</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>4585</v>
       </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
         <v>33</v>
       </c>
-      <c r="X14" t="n">
-        <v>0</v>
-      </c>
       <c r="Y14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
         <v>96142</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AC14" t="n">
         <v>287</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AD14" t="n">
         <v>4181</v>
       </c>
-      <c r="AD14" t="n">
-        <v>2</v>
-      </c>
       <c r="AE14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF14" t="n">
         <v>1375</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AG14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1895,93 +1939,96 @@
         <v>1541</v>
       </c>
       <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
         <v>1345240</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>1060</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>11931</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>24557</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>3</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>42053</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>68</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>1787</v>
       </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
       <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
         <v>1379</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>435</v>
       </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
       <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>352</v>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
       <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>289678</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>2319</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>4585</v>
       </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
       <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
         <v>33</v>
       </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
         <v>96355</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AC15" t="n">
         <v>213</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
         <v>4183</v>
       </c>
-      <c r="AD15" t="n">
-        <v>2</v>
-      </c>
       <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1381</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AG15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1995,93 +2042,96 @@
         <v>1542</v>
       </c>
       <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
         <v>1346390</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>1150</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>11935</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>4</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>24569</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>12</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>42085</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>32</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>1788</v>
       </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
       <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
         <v>1379</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>435</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
       <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>352</v>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>291458</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>1780</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>4626</v>
       </c>
-      <c r="V16" t="n">
+      <c r="W16" t="n">
         <v>41</v>
       </c>
-      <c r="W16" t="n">
+      <c r="X16" t="n">
         <v>33</v>
       </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
       <c r="Y16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
         <v>96540</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AC16" t="n">
         <v>185</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AD16" t="n">
         <v>4184</v>
       </c>
-      <c r="AD16" t="n">
-        <v>1</v>
-      </c>
       <c r="AE16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1388</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AG16" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2095,93 +2145,96 @@
         <v>1543</v>
       </c>
       <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
         <v>1347620</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>1230</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>11937</v>
       </c>
-      <c r="F17" t="n">
-        <v>2</v>
-      </c>
       <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
         <v>24574</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>5</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>42133</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>48</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>1788</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>1381</v>
       </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
       <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
         <v>436</v>
       </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
       <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
         <v>352</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
         <v>293323</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>1865</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>4626</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
         <v>33</v>
       </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
       <c r="Y17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
         <v>96793</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC17" t="n">
         <v>253</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
         <v>4191</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE17" t="n">
         <v>7</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AF17" t="n">
         <v>1397</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2195,93 +2248,96 @@
         <v>1544</v>
       </c>
       <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
         <v>1348790</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>1170</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>11938</v>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
         <v>24578</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>4</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>42215</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>82</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>1790</v>
       </c>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
       <c r="M18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" t="n">
         <v>1384</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>436</v>
       </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
       <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>352</v>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>295454</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>2131</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>4628</v>
       </c>
-      <c r="V18" t="n">
-        <v>2</v>
-      </c>
       <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="n">
         <v>33</v>
       </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
         <v>97118</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AC18" t="n">
         <v>325</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AD18" t="n">
         <v>4196</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
         <v>5</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AF18" t="n">
         <v>1410</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AG18" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2295,93 +2351,96 @@
         <v>1545</v>
       </c>
       <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
         <v>1350010</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>1220</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>11939</v>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>24583</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>42262</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>47</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1792</v>
       </c>
-      <c r="L19" t="n">
-        <v>2</v>
-      </c>
       <c r="M19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" t="n">
         <v>1386</v>
       </c>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
       <c r="O19" t="n">
+        <v>2</v>
+      </c>
+      <c r="P19" t="n">
         <v>436</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
       <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
         <v>353</v>
       </c>
-      <c r="R19" t="n">
-        <v>1</v>
-      </c>
       <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
         <v>297057</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>1603</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>4628</v>
       </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
       <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
         <v>33</v>
       </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
       <c r="Y19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>97338</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AC19" t="n">
         <v>220</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AD19" t="n">
         <v>4200</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AE19" t="n">
         <v>4</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AF19" t="n">
         <v>1415</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AG19" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2395,93 +2454,96 @@
         <v>1546</v>
       </c>
       <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
         <v>1351150</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>1140</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>11940</v>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
         <v>24584</v>
       </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
       <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
         <v>42340</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>78</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>1792</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>1386</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>436</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
         <v>353</v>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
         <v>299199</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>2142</v>
       </c>
-      <c r="U20" t="n">
+      <c r="V20" t="n">
         <v>4632</v>
       </c>
-      <c r="V20" t="n">
+      <c r="W20" t="n">
         <v>4</v>
       </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
         <v>33</v>
       </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
         <v>97600</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AC20" t="n">
         <v>262</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AD20" t="n">
         <v>4202</v>
       </c>
-      <c r="AD20" t="n">
-        <v>2</v>
-      </c>
       <c r="AE20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1426</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AG20" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2495,93 +2557,96 @@
         <v>1547</v>
       </c>
       <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
         <v>1352070</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>920</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>11943</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>3</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>24586</v>
       </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
       <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
         <v>42400</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>60</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>1795</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>1388</v>
       </c>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
       <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
         <v>436</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
         <v>353</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
       <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
         <v>301072</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>1873</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>4632</v>
       </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
       <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
         <v>33</v>
       </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
         <v>97868</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AC21" t="n">
         <v>268</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
         <v>4206</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AE21" t="n">
         <v>4</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AF21" t="n">
         <v>1432</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AG21" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2595,93 +2660,96 @@
         <v>1548</v>
       </c>
       <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
         <v>1352980</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>910</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>11943</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>24591</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>5</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>42454</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>54</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>1797</v>
       </c>
-      <c r="L22" t="n">
-        <v>2</v>
-      </c>
       <c r="M22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" t="n">
         <v>1389</v>
       </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
       <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
         <v>436</v>
       </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>353</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>302787</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>1715</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>4632</v>
       </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
       <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>33</v>
       </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
         <v>98070</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
         <v>202</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
         <v>4207</v>
       </c>
-      <c r="AD22" t="n">
-        <v>1</v>
-      </c>
       <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1436</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AG22" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2695,93 +2763,96 @@
         <v>1549</v>
       </c>
       <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
         <v>1353860</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>880</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>11944</v>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
         <v>24594</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>3</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>42511</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>57</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>1798</v>
       </c>
-      <c r="L23" t="n">
-        <v>1</v>
-      </c>
       <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="n">
         <v>1390</v>
       </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
       <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" t="n">
         <v>436</v>
       </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
       <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>353</v>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
         <v>304659</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>1872</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>4632</v>
       </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
       <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
         <v>33</v>
       </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
         <v>98205</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AC23" t="n">
         <v>135</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AD23" t="n">
         <v>4207</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
       <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1440</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AG23" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2795,93 +2866,96 @@
         <v>1550</v>
       </c>
       <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>1354810</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>950</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>11949</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>5</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>24599</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>5</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>42579</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>68</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>1799</v>
       </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
       <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="n">
         <v>1394</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>436</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
       <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>353</v>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
         <v>306478</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>1819</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>4632</v>
       </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
         <v>33</v>
       </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
         <v>98406</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AC24" t="n">
         <v>201</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
         <v>4212</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AE24" t="n">
         <v>5</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AF24" t="n">
         <v>1444</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AG24" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2895,93 +2969,96 @@
         <v>1551</v>
       </c>
       <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
         <v>1355920</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>1110</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>11950</v>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
         <v>24603</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>42640</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>61</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>1800</v>
       </c>
-      <c r="L25" t="n">
-        <v>1</v>
-      </c>
       <c r="M25" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" t="n">
         <v>1396</v>
       </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
       <c r="O25" t="n">
+        <v>2</v>
+      </c>
+      <c r="P25" t="n">
         <v>436</v>
       </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
       <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
         <v>353</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
         <v>308321</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>1843</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>4632</v>
       </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
         <v>33</v>
       </c>
-      <c r="X25" t="n">
-        <v>0</v>
-      </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
         <v>98698</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AC25" t="n">
         <v>292</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
         <v>4216</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AE25" t="n">
         <v>4</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AF25" t="n">
         <v>1451</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AG25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2995,93 +3072,96 @@
         <v>1552</v>
       </c>
       <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
         <v>1356940</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>1020</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>11953</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>24608</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>5</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>42687</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>47</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>1802</v>
       </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
       <c r="M26" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" t="n">
         <v>1396</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>436</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
         <v>353</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
         <v>310245</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>1924</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>4687</v>
       </c>
-      <c r="V26" t="n">
+      <c r="W26" t="n">
         <v>55</v>
       </c>
-      <c r="W26" t="n">
+      <c r="X26" t="n">
         <v>33</v>
       </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
         <v>99000</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AC26" t="n">
         <v>302</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AD26" t="n">
         <v>4218</v>
       </c>
-      <c r="AD26" t="n">
-        <v>2</v>
-      </c>
       <c r="AE26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1465</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AG26" t="n">
         <v>14</v>
       </c>
     </row>
@@ -3095,93 +3175,96 @@
         <v>1553</v>
       </c>
       <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>1357950</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>1010</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>11954</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
       <c r="G27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
         <v>24615</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>7</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>42751</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>64</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>1804</v>
       </c>
-      <c r="L27" t="n">
-        <v>2</v>
-      </c>
       <c r="M27" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" t="n">
         <v>1397</v>
       </c>
-      <c r="N27" t="n">
-        <v>1</v>
-      </c>
       <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="P27" t="n">
         <v>436</v>
       </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
       <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
         <v>353</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
       <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
         <v>312035</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>1790</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>4687</v>
       </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
       <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
         <v>33</v>
       </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
       <c r="Y27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
         <v>99374</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AC27" t="n">
         <v>374</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AD27" t="n">
         <v>4221</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AE27" t="n">
         <v>3</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AF27" t="n">
         <v>1475</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AG27" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3195,93 +3278,96 @@
         <v>1554</v>
       </c>
       <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>1358950</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>1000</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>11955</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
       <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
         <v>24618</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>3</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>42790</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>39</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>1805</v>
       </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
       <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
         <v>1397</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
       <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>436</v>
       </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
       <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
         <v>353</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
         <v>313342</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>1307</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>4687</v>
       </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
       <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
         <v>33</v>
       </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
       <c r="Y28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
         <v>99645</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AC28" t="n">
         <v>271</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
         <v>4224</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AE28" t="n">
         <v>3</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AF28" t="n">
         <v>1485</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AG28" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3295,93 +3381,96 @@
         <v>1555</v>
       </c>
       <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
         <v>1360110</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>1160</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>11956</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
       <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
         <v>24625</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>7</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>42832</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>42</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>1806</v>
       </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
       <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
         <v>1397</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
       <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
         <v>436</v>
       </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
       <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
         <v>353</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
       <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
         <v>314902</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>1560</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>4687</v>
       </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
       <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
         <v>33</v>
       </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
       <c r="Y29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
         <v>99906</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AC29" t="n">
         <v>261</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AD29" t="n">
         <v>4227</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AE29" t="n">
         <v>3</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AF29" t="n">
         <v>1492</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AG29" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3395,93 +3484,96 @@
         <v>1556</v>
       </c>
       <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
         <v>1361070</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>960</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>11958</v>
       </c>
-      <c r="F30" t="n">
-        <v>2</v>
-      </c>
       <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
         <v>24636</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>11</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>42860</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>28</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1808</v>
       </c>
-      <c r="L30" t="n">
-        <v>2</v>
-      </c>
       <c r="M30" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" t="n">
         <v>1397</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
       <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>436</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
       <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>353</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
         <v>316652</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>1750</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>4687</v>
       </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
       <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
         <v>33</v>
       </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
         <v>100230</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AC30" t="n">
         <v>324</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AD30" t="n">
         <v>4227</v>
       </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
       <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
         <v>1496</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AG30" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3495,93 +3587,96 @@
         <v>1557</v>
       </c>
       <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
         <v>1362500</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>1430</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>11960</v>
       </c>
-      <c r="F31" t="n">
-        <v>2</v>
-      </c>
       <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
         <v>24643</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>7</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>42930</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>70</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>1813</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>5</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>1398</v>
       </c>
-      <c r="N31" t="n">
-        <v>1</v>
-      </c>
       <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
         <v>436</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
       <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>353</v>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
       <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
         <v>318433</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>1781</v>
       </c>
-      <c r="U31" t="n">
+      <c r="V31" t="n">
         <v>4693</v>
       </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
         <v>6</v>
       </c>
-      <c r="W31" t="n">
+      <c r="X31" t="n">
         <v>33</v>
       </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
       <c r="Y31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
         <v>100713</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
         <v>483</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="n">
         <v>4231</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AE31" t="n">
         <v>4</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AF31" t="n">
         <v>1500</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AG31" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3595,93 +3690,96 @@
         <v>1558</v>
       </c>
       <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
         <v>1364060</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>1560</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>11962</v>
       </c>
-      <c r="F32" t="n">
-        <v>2</v>
-      </c>
       <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
         <v>24657</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>14</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>42987</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>57</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>1819</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>6</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>1399</v>
       </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
       <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
         <v>436</v>
       </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
       <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>353</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
         <v>320327</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>1894</v>
       </c>
-      <c r="U32" t="n">
+      <c r="V32" t="n">
         <v>4693</v>
       </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
       <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
         <v>33</v>
       </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
         <v>101237</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AC32" t="n">
         <v>524</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AD32" t="n">
         <v>4234</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AE32" t="n">
         <v>3</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AF32" t="n">
         <v>1519</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AG32" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3695,53 +3793,53 @@
         <v>1564</v>
       </c>
       <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
         <v>1372270</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>8210</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>11983</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>21</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>24696</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>39</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>43397</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>410</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>1405</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>6</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>436</v>
       </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
       <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
         <v>353</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
@@ -3755,34 +3853,140 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
         <v>33</v>
       </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
       <c r="Y33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
         <v>103658</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
         <v>2421</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AD33" t="n">
         <v>4253</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="n">
         <v>19</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AF33" t="n">
         <v>1585</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AG33" t="n">
         <v>66</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1565</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1373620</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F34" t="n">
+        <v>11989</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="n">
+        <v>24700</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>43479</v>
+      </c>
+      <c r="K34" t="n">
+        <v>82</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1407</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>353</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>104051</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>393</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>4257</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1595</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG34"/>
+  <dimension ref="A1:AG39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3987,6 +3987,521 @@
       </c>
       <c r="AG34" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1559</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1365470</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1410</v>
+      </c>
+      <c r="F35" t="n">
+        <v>11966</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>24659</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>43037</v>
+      </c>
+      <c r="K35" t="n">
+        <v>50</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1820</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1399</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>353</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>322179</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1852</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4693</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>101621</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>384</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>4239</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1528</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1560</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1366910</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11969</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>24666</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>43112</v>
+      </c>
+      <c r="K36" t="n">
+        <v>75</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1821</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1400</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>353</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>323762</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1583</v>
+      </c>
+      <c r="V36" t="n">
+        <v>4693</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>102138</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>517</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>4241</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1542</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1561</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1368040</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1130</v>
+      </c>
+      <c r="F37" t="n">
+        <v>11974</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>24673</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" t="n">
+        <v>43172</v>
+      </c>
+      <c r="K37" t="n">
+        <v>60</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1826</v>
+      </c>
+      <c r="M37" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1403</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>353</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>325615</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1853</v>
+      </c>
+      <c r="V37" t="n">
+        <v>4733</v>
+      </c>
+      <c r="W37" t="n">
+        <v>40</v>
+      </c>
+      <c r="X37" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>102575</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>437</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>4245</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1548</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1562</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1369340</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11978</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>24676</v>
+      </c>
+      <c r="I38" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>43247</v>
+      </c>
+      <c r="K38" t="n">
+        <v>75</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1830</v>
+      </c>
+      <c r="M38" t="n">
+        <v>4</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1403</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>353</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>327726</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2111</v>
+      </c>
+      <c r="V38" t="n">
+        <v>4733</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>102971</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>396</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>4248</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1562</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1563</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1370890</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1550</v>
+      </c>
+      <c r="F39" t="n">
+        <v>11980</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" t="n">
+        <v>24684</v>
+      </c>
+      <c r="I39" t="n">
+        <v>8</v>
+      </c>
+      <c r="J39" t="n">
+        <v>43315</v>
+      </c>
+      <c r="K39" t="n">
+        <v>68</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1832</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1404</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>353</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>329772</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2046</v>
+      </c>
+      <c r="V39" t="n">
+        <v>4733</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>103300</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>329</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>4250</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1576</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG39"/>
+  <dimension ref="A1:AG40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4502,6 +4502,109 @@
       </c>
       <c r="AG39" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1566</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1374950</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F40" t="n">
+        <v>11997</v>
+      </c>
+      <c r="G40" t="n">
+        <v>8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>24705</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>43564</v>
+      </c>
+      <c r="K40" t="n">
+        <v>85</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1409</v>
+      </c>
+      <c r="O40" t="n">
+        <v>2</v>
+      </c>
+      <c r="P40" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>353</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>104414</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>363</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>4259</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1607</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG40"/>
+  <dimension ref="A1:AG41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4605,6 +4605,109 @@
       </c>
       <c r="AG40" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1567</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1376320</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F41" t="n">
+        <v>12001</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" t="n">
+        <v>24710</v>
+      </c>
+      <c r="I41" t="n">
+        <v>5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>43639</v>
+      </c>
+      <c r="K41" t="n">
+        <v>75</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>1411</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>353</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>104796</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>382</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>4263</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1614</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG41"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4708,6 +4708,109 @@
       </c>
       <c r="AG41" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1568</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1377510</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1280</v>
+      </c>
+      <c r="F42" t="n">
+        <v>12004</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" t="n">
+        <v>24717</v>
+      </c>
+      <c r="I42" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>43713</v>
+      </c>
+      <c r="K42" t="n">
+        <v>74</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1414</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>353</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>105172</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>379</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>4267</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1619</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG42"/>
+  <dimension ref="A1:AG43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4811,6 +4811,109 @@
       </c>
       <c r="AG42" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1569</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1378820</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12010</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" t="n">
+        <v>24727</v>
+      </c>
+      <c r="I43" t="n">
+        <v>10</v>
+      </c>
+      <c r="J43" t="n">
+        <v>43787</v>
+      </c>
+      <c r="K43" t="n">
+        <v>74</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1859</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1416</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2</v>
+      </c>
+      <c r="P43" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>353</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>342651</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2120</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>105498</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>326</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>4277</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>1628</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG43"/>
+  <dimension ref="A1:AG44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4914,6 +4914,109 @@
       </c>
       <c r="AG43" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1570</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1380120</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F44" t="n">
+        <v>12014</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24728</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>43865</v>
+      </c>
+      <c r="K44" t="n">
+        <v>78</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1861</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1417</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>353</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>344869</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2218</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>105850</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>352</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>4280</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1636</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG44"/>
+  <dimension ref="A1:AG45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5017,6 +5017,109 @@
       </c>
       <c r="AG44" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1571</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1381430</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F45" t="n">
+        <v>12015</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>24739</v>
+      </c>
+      <c r="I45" t="n">
+        <v>11</v>
+      </c>
+      <c r="J45" t="n">
+        <v>43953</v>
+      </c>
+      <c r="K45" t="n">
+        <v>88</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1865</v>
+      </c>
+      <c r="M45" t="n">
+        <v>4</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1418</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>353</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>347033</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2164</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>106274</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>424</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>4287</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1648</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG45"/>
+  <dimension ref="A1:AG46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5120,6 +5120,109 @@
       </c>
       <c r="AG45" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1572</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1382870</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F46" t="n">
+        <v>12020</v>
+      </c>
+      <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>24753</v>
+      </c>
+      <c r="I46" t="n">
+        <v>14</v>
+      </c>
+      <c r="J46" t="n">
+        <v>44010</v>
+      </c>
+      <c r="K46" t="n">
+        <v>57</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1868</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1419</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>353</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>349165</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2132</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>106675</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>401</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>4288</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1661</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG46"/>
+  <dimension ref="A1:AG47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5223,6 +5223,109 @@
       </c>
       <c r="AG46" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1573</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1384190</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F47" t="n">
+        <v>12025</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>24763</v>
+      </c>
+      <c r="I47" t="n">
+        <v>10</v>
+      </c>
+      <c r="J47" t="n">
+        <v>44082</v>
+      </c>
+      <c r="K47" t="n">
+        <v>72</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1870</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1420</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>353</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>351479</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2314</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>107091</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>416</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>4296</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1664</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG47"/>
+  <dimension ref="A1:AG48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5325,6 +5325,109 @@
         <v>1664</v>
       </c>
       <c r="AG47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1574</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1385420</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F48" t="n">
+        <v>12026</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>24768</v>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>44118</v>
+      </c>
+      <c r="K48" t="n">
+        <v>36</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1872</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1427</v>
+      </c>
+      <c r="O48" t="n">
+        <v>7</v>
+      </c>
+      <c r="P48" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>353</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>353541</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2062</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>107508</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>417</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>4300</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1667</v>
+      </c>
+      <c r="AG48" t="n">
         <v>3</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG48"/>
+  <dimension ref="A1:AG49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5429,6 +5429,109 @@
       </c>
       <c r="AG48" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1575</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1386680</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12033</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7</v>
+      </c>
+      <c r="H49" t="n">
+        <v>24775</v>
+      </c>
+      <c r="I49" t="n">
+        <v>7</v>
+      </c>
+      <c r="J49" t="n">
+        <v>44169</v>
+      </c>
+      <c r="K49" t="n">
+        <v>51</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1874</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" t="n">
+        <v>1427</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>353</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>355593</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2052</v>
+      </c>
+      <c r="V49" t="n">
+        <v>4783</v>
+      </c>
+      <c r="W49" t="n">
+        <v>50</v>
+      </c>
+      <c r="X49" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>107994</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>486</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>4303</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1677</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG49"/>
+  <dimension ref="A1:AG50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5532,6 +5532,109 @@
       </c>
       <c r="AG49" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1576</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1388050</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F50" t="n">
+        <v>12038</v>
+      </c>
+      <c r="G50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H50" t="n">
+        <v>24779</v>
+      </c>
+      <c r="I50" t="n">
+        <v>4</v>
+      </c>
+      <c r="J50" t="n">
+        <v>44240</v>
+      </c>
+      <c r="K50" t="n">
+        <v>71</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1877</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3</v>
+      </c>
+      <c r="N50" t="n">
+        <v>1431</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4</v>
+      </c>
+      <c r="P50" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>353</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>357589</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1996</v>
+      </c>
+      <c r="V50" t="n">
+        <v>4783</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>108425</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>431</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>4306</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>1684</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG50"/>
+  <dimension ref="A1:AG51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5635,6 +5635,109 @@
       </c>
       <c r="AG50" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1577</v>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1389420</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F51" t="n">
+        <v>12040</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>24783</v>
+      </c>
+      <c r="I51" t="n">
+        <v>4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>44298</v>
+      </c>
+      <c r="K51" t="n">
+        <v>58</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1881</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4</v>
+      </c>
+      <c r="N51" t="n">
+        <v>1432</v>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>353</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>359557</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1968</v>
+      </c>
+      <c r="V51" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W51" t="n">
+        <v>4</v>
+      </c>
+      <c r="X51" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>108866</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>441</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>4309</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>1688</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG51"/>
+  <dimension ref="A1:AG52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5738,6 +5738,109 @@
       </c>
       <c r="AG51" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1578</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1390660</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F52" t="n">
+        <v>12041</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>24787</v>
+      </c>
+      <c r="I52" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>44386</v>
+      </c>
+      <c r="K52" t="n">
+        <v>88</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1883</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" t="n">
+        <v>1433</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>353</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>361803</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2246</v>
+      </c>
+      <c r="V52" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>109342</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>476</v>
+      </c>
+      <c r="AD52" t="n">
+        <v>4314</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>1695</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG52"/>
+  <dimension ref="A1:AG56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5840,6 +5840,418 @@
         <v>1695</v>
       </c>
       <c r="AG52" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1579</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1391950</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F53" t="n">
+        <v>12049</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8</v>
+      </c>
+      <c r="H53" t="n">
+        <v>24797</v>
+      </c>
+      <c r="I53" t="n">
+        <v>10</v>
+      </c>
+      <c r="J53" t="n">
+        <v>44479</v>
+      </c>
+      <c r="K53" t="n">
+        <v>93</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1885</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" t="n">
+        <v>1435</v>
+      </c>
+      <c r="O53" t="n">
+        <v>2</v>
+      </c>
+      <c r="P53" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>353</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>364149</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2346</v>
+      </c>
+      <c r="V53" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>109817</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>475</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>4316</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>1703</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1393140</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F54" t="n">
+        <v>12050</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>24805</v>
+      </c>
+      <c r="I54" t="n">
+        <v>8</v>
+      </c>
+      <c r="J54" t="n">
+        <v>44530</v>
+      </c>
+      <c r="K54" t="n">
+        <v>51</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1886</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>1437</v>
+      </c>
+      <c r="O54" t="n">
+        <v>2</v>
+      </c>
+      <c r="P54" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>353</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>366164</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2015</v>
+      </c>
+      <c r="V54" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>110201</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>384</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>4321</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1712</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1581</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1394530</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F55" t="n">
+        <v>12050</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>24812</v>
+      </c>
+      <c r="I55" t="n">
+        <v>7</v>
+      </c>
+      <c r="J55" t="n">
+        <v>44604</v>
+      </c>
+      <c r="K55" t="n">
+        <v>74</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1887</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>1437</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>353</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>368015</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1851</v>
+      </c>
+      <c r="V55" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>110827</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>626</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>4329</v>
+      </c>
+      <c r="AE55" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF55" t="n">
+        <v>1719</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1582</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1395790</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F56" t="n">
+        <v>12056</v>
+      </c>
+      <c r="G56" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" t="n">
+        <v>24816</v>
+      </c>
+      <c r="I56" t="n">
+        <v>4</v>
+      </c>
+      <c r="J56" t="n">
+        <v>44664</v>
+      </c>
+      <c r="K56" t="n">
+        <v>60</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1889</v>
+      </c>
+      <c r="M56" t="n">
+        <v>2</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1440</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3</v>
+      </c>
+      <c r="P56" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>353</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>369888</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1873</v>
+      </c>
+      <c r="V56" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>111257</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>430</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>4333</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>1726</v>
+      </c>
+      <c r="AG56" t="n">
         <v>7</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG56"/>
+  <dimension ref="A1:AG57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6253,6 +6253,109 @@
       </c>
       <c r="AG56" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1583</v>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1397060</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1270</v>
+      </c>
+      <c r="F57" t="n">
+        <v>12057</v>
+      </c>
+      <c r="G57" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" t="n">
+        <v>24818</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" t="n">
+        <v>44731</v>
+      </c>
+      <c r="K57" t="n">
+        <v>67</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1893</v>
+      </c>
+      <c r="M57" t="n">
+        <v>4</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1443</v>
+      </c>
+      <c r="O57" t="n">
+        <v>3</v>
+      </c>
+      <c r="P57" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>353</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>371882</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1994</v>
+      </c>
+      <c r="V57" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>111707</v>
+      </c>
+      <c r="AC57" t="n">
+        <v>450</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>4339</v>
+      </c>
+      <c r="AE57" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF57" t="n">
+        <v>1728</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG57"/>
+  <dimension ref="A1:AG58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6356,6 +6356,109 @@
       </c>
       <c r="AG57" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1584</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1398370</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F58" t="n">
+        <v>12059</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>24823</v>
+      </c>
+      <c r="I58" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>44799</v>
+      </c>
+      <c r="K58" t="n">
+        <v>68</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1896</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1447</v>
+      </c>
+      <c r="O58" t="n">
+        <v>4</v>
+      </c>
+      <c r="P58" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>353</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>373660</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1778</v>
+      </c>
+      <c r="V58" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>112146</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>439</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>4348</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>1729</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AG59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6459,6 +6459,109 @@
       </c>
       <c r="AG58" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1585</v>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1399720</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F59" t="n">
+        <v>12060</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" t="n">
+        <v>24835</v>
+      </c>
+      <c r="I59" t="n">
+        <v>12</v>
+      </c>
+      <c r="J59" t="n">
+        <v>44857</v>
+      </c>
+      <c r="K59" t="n">
+        <v>58</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1899</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1447</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>353</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>375611</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1951</v>
+      </c>
+      <c r="V59" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>112634</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>488</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>4353</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG59"/>
+  <dimension ref="A1:AG60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6562,6 +6562,109 @@
       </c>
       <c r="AG59" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1586</v>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1400970</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F60" t="n">
+        <v>12063</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" t="n">
+        <v>24844</v>
+      </c>
+      <c r="I60" t="n">
+        <v>9</v>
+      </c>
+      <c r="J60" t="n">
+        <v>44920</v>
+      </c>
+      <c r="K60" t="n">
+        <v>63</v>
+      </c>
+      <c r="L60" t="n">
+        <v>1901</v>
+      </c>
+      <c r="M60" t="n">
+        <v>2</v>
+      </c>
+      <c r="N60" t="n">
+        <v>1454</v>
+      </c>
+      <c r="O60" t="n">
+        <v>7</v>
+      </c>
+      <c r="P60" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>353</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>377500</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1889</v>
+      </c>
+      <c r="V60" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>113135</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>501</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>4360</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>1754</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG60"/>
+  <dimension ref="A1:AG61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6665,6 +6665,109 @@
       </c>
       <c r="AG60" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1587</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1402200</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F61" t="n">
+        <v>12066</v>
+      </c>
+      <c r="G61" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>24845</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>44969</v>
+      </c>
+      <c r="K61" t="n">
+        <v>49</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1901</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>1454</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>353</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>379224</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1724</v>
+      </c>
+      <c r="V61" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>113612</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>477</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>4366</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>1764</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG61"/>
+  <dimension ref="A1:AG62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6768,6 +6768,109 @@
       </c>
       <c r="AG61" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1588</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1403550</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F62" t="n">
+        <v>12067</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>24851</v>
+      </c>
+      <c r="I62" t="n">
+        <v>6</v>
+      </c>
+      <c r="J62" t="n">
+        <v>45040</v>
+      </c>
+      <c r="K62" t="n">
+        <v>71</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1901</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="n">
+        <v>1455</v>
+      </c>
+      <c r="O62" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>353</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>381176</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1952</v>
+      </c>
+      <c r="V62" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W62" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>114104</v>
+      </c>
+      <c r="AC62" t="n">
+        <v>492</v>
+      </c>
+      <c r="AD62" t="n">
+        <v>4368</v>
+      </c>
+      <c r="AE62" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF62" t="n">
+        <v>1777</v>
+      </c>
+      <c r="AG62" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6871,6 +6871,109 @@
       </c>
       <c r="AG62" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1589</v>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1404760</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1210</v>
+      </c>
+      <c r="F63" t="n">
+        <v>12069</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" t="n">
+        <v>24856</v>
+      </c>
+      <c r="I63" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>45111</v>
+      </c>
+      <c r="K63" t="n">
+        <v>71</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1903</v>
+      </c>
+      <c r="M63" t="n">
+        <v>2</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1459</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4</v>
+      </c>
+      <c r="P63" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>353</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>383067</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1891</v>
+      </c>
+      <c r="V63" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>114499</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>395</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>4369</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>1782</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6974,6 +6974,109 @@
       </c>
       <c r="AG63" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1590</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1405900</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1140</v>
+      </c>
+      <c r="F64" t="n">
+        <v>12069</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>24861</v>
+      </c>
+      <c r="I64" t="n">
+        <v>5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>45168</v>
+      </c>
+      <c r="K64" t="n">
+        <v>57</v>
+      </c>
+      <c r="L64" t="n">
+        <v>1910</v>
+      </c>
+      <c r="M64" t="n">
+        <v>7</v>
+      </c>
+      <c r="N64" t="n">
+        <v>1459</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>353</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>385190</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2123</v>
+      </c>
+      <c r="V64" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W64" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>114852</v>
+      </c>
+      <c r="AC64" t="n">
+        <v>353</v>
+      </c>
+      <c r="AD64" t="n">
+        <v>4376</v>
+      </c>
+      <c r="AE64" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF64" t="n">
+        <v>1791</v>
+      </c>
+      <c r="AG64" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7077,6 +7077,109 @@
       </c>
       <c r="AG64" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1591</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1407150</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1250</v>
+      </c>
+      <c r="F65" t="n">
+        <v>12073</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4</v>
+      </c>
+      <c r="H65" t="n">
+        <v>24863</v>
+      </c>
+      <c r="I65" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" t="n">
+        <v>45225</v>
+      </c>
+      <c r="K65" t="n">
+        <v>57</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1912</v>
+      </c>
+      <c r="M65" t="n">
+        <v>2</v>
+      </c>
+      <c r="N65" t="n">
+        <v>1463</v>
+      </c>
+      <c r="O65" t="n">
+        <v>4</v>
+      </c>
+      <c r="P65" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>353</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>387342</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2152</v>
+      </c>
+      <c r="V65" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>115237</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>385</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>4380</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1809</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG65"/>
+  <dimension ref="A1:AG66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7180,6 +7180,109 @@
       </c>
       <c r="AG65" t="n">
         <v>18</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1592</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1408340</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F66" t="n">
+        <v>12074</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" t="n">
+        <v>24869</v>
+      </c>
+      <c r="I66" t="n">
+        <v>6</v>
+      </c>
+      <c r="J66" t="n">
+        <v>45325</v>
+      </c>
+      <c r="K66" t="n">
+        <v>100</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1913</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>1469</v>
+      </c>
+      <c r="O66" t="n">
+        <v>6</v>
+      </c>
+      <c r="P66" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>353</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>389110</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1768</v>
+      </c>
+      <c r="V66" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W66" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>115644</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>407</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>4385</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1815</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG66"/>
+  <dimension ref="A1:AG67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7282,6 +7282,109 @@
         <v>1815</v>
       </c>
       <c r="AG66" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1593</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1409630</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1290</v>
+      </c>
+      <c r="F67" t="n">
+        <v>12081</v>
+      </c>
+      <c r="G67" t="n">
+        <v>7</v>
+      </c>
+      <c r="H67" t="n">
+        <v>24878</v>
+      </c>
+      <c r="I67" t="n">
+        <v>9</v>
+      </c>
+      <c r="J67" t="n">
+        <v>45388</v>
+      </c>
+      <c r="K67" t="n">
+        <v>63</v>
+      </c>
+      <c r="L67" t="n">
+        <v>1916</v>
+      </c>
+      <c r="M67" t="n">
+        <v>3</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1470</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="R67" t="n">
+        <v>353</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>390738</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1628</v>
+      </c>
+      <c r="V67" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0</v>
+      </c>
+      <c r="X67" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>116106</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>462</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>4385</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1821</v>
+      </c>
+      <c r="AG67" t="n">
         <v>6</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG67"/>
+  <dimension ref="A1:AG68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7386,6 +7386,109 @@
       </c>
       <c r="AG67" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1594</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1411050</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F68" t="n">
+        <v>12088</v>
+      </c>
+      <c r="G68" t="n">
+        <v>7</v>
+      </c>
+      <c r="H68" t="n">
+        <v>24894</v>
+      </c>
+      <c r="I68" t="n">
+        <v>16</v>
+      </c>
+      <c r="J68" t="n">
+        <v>45451</v>
+      </c>
+      <c r="K68" t="n">
+        <v>63</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1917</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1473</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3</v>
+      </c>
+      <c r="P68" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>353</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>392717</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1979</v>
+      </c>
+      <c r="V68" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>116686</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>580</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>4389</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1833</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG68"/>
+  <dimension ref="A1:AG69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7489,6 +7489,109 @@
       </c>
       <c r="AG68" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1595</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1412250</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F69" t="n">
+        <v>12097</v>
+      </c>
+      <c r="G69" t="n">
+        <v>9</v>
+      </c>
+      <c r="H69" t="n">
+        <v>24899</v>
+      </c>
+      <c r="I69" t="n">
+        <v>5</v>
+      </c>
+      <c r="J69" t="n">
+        <v>45508</v>
+      </c>
+      <c r="K69" t="n">
+        <v>57</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1917</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1478</v>
+      </c>
+      <c r="O69" t="n">
+        <v>5</v>
+      </c>
+      <c r="P69" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>353</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>394846</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2129</v>
+      </c>
+      <c r="V69" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0</v>
+      </c>
+      <c r="X69" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>117085</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>399</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>4394</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1848</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG69"/>
+  <dimension ref="A1:AG70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7592,6 +7592,109 @@
       </c>
       <c r="AG69" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1596</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1413510</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F70" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G70" t="n">
+        <v>3</v>
+      </c>
+      <c r="H70" t="n">
+        <v>24903</v>
+      </c>
+      <c r="I70" t="n">
+        <v>4</v>
+      </c>
+      <c r="J70" t="n">
+        <v>45569</v>
+      </c>
+      <c r="K70" t="n">
+        <v>61</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1918</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1478</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>353</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>396920</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2074</v>
+      </c>
+      <c r="V70" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0</v>
+      </c>
+      <c r="X70" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>117547</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>462</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>4398</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1853</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG70"/>
+  <dimension ref="A1:AG71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7695,6 +7695,109 @@
       </c>
       <c r="AG70" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1597</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1414820</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F71" t="n">
+        <v>12107</v>
+      </c>
+      <c r="G71" t="n">
+        <v>7</v>
+      </c>
+      <c r="H71" t="n">
+        <v>24906</v>
+      </c>
+      <c r="I71" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>45628</v>
+      </c>
+      <c r="K71" t="n">
+        <v>59</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1922</v>
+      </c>
+      <c r="M71" t="n">
+        <v>4</v>
+      </c>
+      <c r="N71" t="n">
+        <v>1479</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>353</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>398763</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1843</v>
+      </c>
+      <c r="V71" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>117910</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>363</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>4402</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1857</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG71"/>
+  <dimension ref="A1:AG72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7798,6 +7798,109 @@
       </c>
       <c r="AG71" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1598</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1416280</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F72" t="n">
+        <v>12108</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>24912</v>
+      </c>
+      <c r="I72" t="n">
+        <v>6</v>
+      </c>
+      <c r="J72" t="n">
+        <v>45680</v>
+      </c>
+      <c r="K72" t="n">
+        <v>52</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1923</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1481</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2</v>
+      </c>
+      <c r="P72" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>353</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>400631</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1868</v>
+      </c>
+      <c r="V72" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>118249</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>339</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>4402</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1865</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG72"/>
+  <dimension ref="A1:AG73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7901,6 +7901,109 @@
       </c>
       <c r="AG72" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1599</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1417770</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F73" t="n">
+        <v>12116</v>
+      </c>
+      <c r="G73" t="n">
+        <v>8</v>
+      </c>
+      <c r="H73" t="n">
+        <v>24922</v>
+      </c>
+      <c r="I73" t="n">
+        <v>10</v>
+      </c>
+      <c r="J73" t="n">
+        <v>45754</v>
+      </c>
+      <c r="K73" t="n">
+        <v>74</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1924</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1</v>
+      </c>
+      <c r="N73" t="n">
+        <v>1485</v>
+      </c>
+      <c r="O73" t="n">
+        <v>4</v>
+      </c>
+      <c r="P73" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>353</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>401925</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1294</v>
+      </c>
+      <c r="V73" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>118610</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>361</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>4402</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>1868</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG73"/>
+  <dimension ref="A1:AG74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8004,6 +8004,109 @@
       </c>
       <c r="AG73" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1419090</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F74" t="n">
+        <v>12120</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4</v>
+      </c>
+      <c r="H74" t="n">
+        <v>24928</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6</v>
+      </c>
+      <c r="J74" t="n">
+        <v>45807</v>
+      </c>
+      <c r="K74" t="n">
+        <v>53</v>
+      </c>
+      <c r="L74" t="n">
+        <v>1928</v>
+      </c>
+      <c r="M74" t="n">
+        <v>4</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1485</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>353</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>403959</v>
+      </c>
+      <c r="U74" t="n">
+        <v>2034</v>
+      </c>
+      <c r="V74" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W74" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>119038</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>428</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>4407</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>1883</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG74"/>
+  <dimension ref="A1:AG75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8107,6 +8107,109 @@
       </c>
       <c r="AG74" t="n">
         <v>15</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1601</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1420690</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F75" t="n">
+        <v>12125</v>
+      </c>
+      <c r="G75" t="n">
+        <v>5</v>
+      </c>
+      <c r="H75" t="n">
+        <v>24931</v>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>45865</v>
+      </c>
+      <c r="K75" t="n">
+        <v>58</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1929</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1489</v>
+      </c>
+      <c r="O75" t="n">
+        <v>4</v>
+      </c>
+      <c r="P75" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>353</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>405693</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1734</v>
+      </c>
+      <c r="V75" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>119532</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>494</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>4412</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1894</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG75"/>
+  <dimension ref="A1:AG76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8209,6 +8209,109 @@
         <v>1894</v>
       </c>
       <c r="AG75" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1602</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1421810</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F76" t="n">
+        <v>12131</v>
+      </c>
+      <c r="G76" t="n">
+        <v>6</v>
+      </c>
+      <c r="H76" t="n">
+        <v>24932</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="n">
+        <v>45911</v>
+      </c>
+      <c r="K76" t="n">
+        <v>46</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1931</v>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1491</v>
+      </c>
+      <c r="O76" t="n">
+        <v>2</v>
+      </c>
+      <c r="P76" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="R76" t="n">
+        <v>353</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>407201</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1508</v>
+      </c>
+      <c r="V76" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W76" t="n">
+        <v>0</v>
+      </c>
+      <c r="X76" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>119862</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>330</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>4416</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>1905</v>
+      </c>
+      <c r="AG76" t="n">
         <v>11</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG76"/>
+  <dimension ref="A1:AG77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8313,6 +8313,109 @@
       </c>
       <c r="AG76" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1423280</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F77" t="n">
+        <v>12141</v>
+      </c>
+      <c r="G77" t="n">
+        <v>10</v>
+      </c>
+      <c r="H77" t="n">
+        <v>24938</v>
+      </c>
+      <c r="I77" t="n">
+        <v>6</v>
+      </c>
+      <c r="J77" t="n">
+        <v>45953</v>
+      </c>
+      <c r="K77" t="n">
+        <v>42</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1936</v>
+      </c>
+      <c r="M77" t="n">
+        <v>5</v>
+      </c>
+      <c r="N77" t="n">
+        <v>1492</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="R77" t="n">
+        <v>353</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>409204</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2003</v>
+      </c>
+      <c r="V77" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W77" t="n">
+        <v>0</v>
+      </c>
+      <c r="X77" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>120307</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>445</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>4420</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>1907</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG77"/>
+  <dimension ref="A1:AG78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8416,6 +8416,109 @@
       </c>
       <c r="AG77" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1604</v>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1424620</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1340</v>
+      </c>
+      <c r="F78" t="n">
+        <v>12144</v>
+      </c>
+      <c r="G78" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" t="n">
+        <v>24940</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>46019</v>
+      </c>
+      <c r="K78" t="n">
+        <v>66</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1936</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1492</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="n">
+        <v>353</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>411005</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1801</v>
+      </c>
+      <c r="V78" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W78" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>120727</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>420</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>4420</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>1919</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG78"/>
+  <dimension ref="A1:AG79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8519,6 +8519,109 @@
       </c>
       <c r="AG78" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1605</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1425990</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F79" t="n">
+        <v>12148</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4</v>
+      </c>
+      <c r="H79" t="n">
+        <v>24946</v>
+      </c>
+      <c r="I79" t="n">
+        <v>6</v>
+      </c>
+      <c r="J79" t="n">
+        <v>46084</v>
+      </c>
+      <c r="K79" t="n">
+        <v>65</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1943</v>
+      </c>
+      <c r="M79" t="n">
+        <v>7</v>
+      </c>
+      <c r="N79" t="n">
+        <v>1496</v>
+      </c>
+      <c r="O79" t="n">
+        <v>4</v>
+      </c>
+      <c r="P79" t="n">
+        <v>437</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>354</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>412884</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1879</v>
+      </c>
+      <c r="V79" t="n">
+        <v>4787</v>
+      </c>
+      <c r="W79" t="n">
+        <v>0</v>
+      </c>
+      <c r="X79" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>121216</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>489</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>4424</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>1932</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG79"/>
+  <dimension ref="A1:AG80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8622,6 +8622,109 @@
       </c>
       <c r="AG79" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1606</v>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1427410</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F80" t="n">
+        <v>12151</v>
+      </c>
+      <c r="G80" t="n">
+        <v>3</v>
+      </c>
+      <c r="H80" t="n">
+        <v>24956</v>
+      </c>
+      <c r="I80" t="n">
+        <v>10</v>
+      </c>
+      <c r="J80" t="n">
+        <v>46169</v>
+      </c>
+      <c r="K80" t="n">
+        <v>85</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1946</v>
+      </c>
+      <c r="M80" t="n">
+        <v>3</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1502</v>
+      </c>
+      <c r="O80" t="n">
+        <v>6</v>
+      </c>
+      <c r="P80" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1</v>
+      </c>
+      <c r="R80" t="n">
+        <v>354</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>414798</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1914</v>
+      </c>
+      <c r="V80" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>121742</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>526</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>4428</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>1943</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG80"/>
+  <dimension ref="A1:AG81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8725,6 +8725,109 @@
       </c>
       <c r="AG80" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1607</v>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1428930</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F81" t="n">
+        <v>12156</v>
+      </c>
+      <c r="G81" t="n">
+        <v>5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>24963</v>
+      </c>
+      <c r="I81" t="n">
+        <v>7</v>
+      </c>
+      <c r="J81" t="n">
+        <v>46261</v>
+      </c>
+      <c r="K81" t="n">
+        <v>92</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1950</v>
+      </c>
+      <c r="M81" t="n">
+        <v>4</v>
+      </c>
+      <c r="N81" t="n">
+        <v>1505</v>
+      </c>
+      <c r="O81" t="n">
+        <v>3</v>
+      </c>
+      <c r="P81" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>354</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>416656</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1858</v>
+      </c>
+      <c r="V81" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W81" t="n">
+        <v>0</v>
+      </c>
+      <c r="X81" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>122289</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>547</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>4430</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>1956</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG81"/>
+  <dimension ref="A1:AG82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8828,6 +8828,109 @@
       </c>
       <c r="AG81" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1608</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1430530</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F82" t="n">
+        <v>12158</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" t="n">
+        <v>24971</v>
+      </c>
+      <c r="I82" t="n">
+        <v>8</v>
+      </c>
+      <c r="J82" t="n">
+        <v>46343</v>
+      </c>
+      <c r="K82" t="n">
+        <v>82</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1953</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1511</v>
+      </c>
+      <c r="O82" t="n">
+        <v>6</v>
+      </c>
+      <c r="P82" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>354</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>418425</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1769</v>
+      </c>
+      <c r="V82" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W82" t="n">
+        <v>0</v>
+      </c>
+      <c r="X82" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>122894</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>605</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>4433</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>1965</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG82"/>
+  <dimension ref="A1:AG83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8931,6 +8931,109 @@
       </c>
       <c r="AG82" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1609</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1431900</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F83" t="n">
+        <v>12161</v>
+      </c>
+      <c r="G83" t="n">
+        <v>3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>24978</v>
+      </c>
+      <c r="I83" t="n">
+        <v>7</v>
+      </c>
+      <c r="J83" t="n">
+        <v>46435</v>
+      </c>
+      <c r="K83" t="n">
+        <v>92</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1955</v>
+      </c>
+      <c r="M83" t="n">
+        <v>2</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1513</v>
+      </c>
+      <c r="O83" t="n">
+        <v>2</v>
+      </c>
+      <c r="P83" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" t="n">
+        <v>354</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>420290</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1865</v>
+      </c>
+      <c r="V83" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W83" t="n">
+        <v>0</v>
+      </c>
+      <c r="X83" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>123347</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>453</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>4441</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>1970</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG83"/>
+  <dimension ref="A1:AG84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9034,6 +9034,109 @@
       </c>
       <c r="AG83" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1610</v>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1433230</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F84" t="n">
+        <v>12163</v>
+      </c>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
+      <c r="H84" t="n">
+        <v>24982</v>
+      </c>
+      <c r="I84" t="n">
+        <v>4</v>
+      </c>
+      <c r="J84" t="n">
+        <v>46492</v>
+      </c>
+      <c r="K84" t="n">
+        <v>57</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1958</v>
+      </c>
+      <c r="M84" t="n">
+        <v>3</v>
+      </c>
+      <c r="N84" t="n">
+        <v>1513</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" t="n">
+        <v>354</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>421900</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1610</v>
+      </c>
+      <c r="V84" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W84" t="n">
+        <v>0</v>
+      </c>
+      <c r="X84" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>123702</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>355</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>4450</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>1981</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG84"/>
+  <dimension ref="A1:AG85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9137,6 +9137,109 @@
       </c>
       <c r="AG84" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1611</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1434690</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12191</v>
+      </c>
+      <c r="G85" t="n">
+        <v>28</v>
+      </c>
+      <c r="H85" t="n">
+        <v>24994</v>
+      </c>
+      <c r="I85" t="n">
+        <v>12</v>
+      </c>
+      <c r="J85" t="n">
+        <v>46570</v>
+      </c>
+      <c r="K85" t="n">
+        <v>78</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1961</v>
+      </c>
+      <c r="M85" t="n">
+        <v>3</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1515</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2</v>
+      </c>
+      <c r="P85" t="n">
+        <v>438</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="n">
+        <v>354</v>
+      </c>
+      <c r="S85" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>423588</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1688</v>
+      </c>
+      <c r="V85" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W85" t="n">
+        <v>0</v>
+      </c>
+      <c r="X85" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>124243</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>541</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>4453</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>1994</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG85"/>
+  <dimension ref="A1:AG86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9240,6 +9240,109 @@
       </c>
       <c r="AG85" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1612</v>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1436100</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1410</v>
+      </c>
+      <c r="F86" t="n">
+        <v>12201</v>
+      </c>
+      <c r="G86" t="n">
+        <v>10</v>
+      </c>
+      <c r="H86" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I86" t="n">
+        <v>6</v>
+      </c>
+      <c r="J86" t="n">
+        <v>46646</v>
+      </c>
+      <c r="K86" t="n">
+        <v>76</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1968</v>
+      </c>
+      <c r="M86" t="n">
+        <v>7</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1516</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1</v>
+      </c>
+      <c r="R86" t="n">
+        <v>354</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>425240</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1652</v>
+      </c>
+      <c r="V86" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W86" t="n">
+        <v>0</v>
+      </c>
+      <c r="X86" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>124787</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>544</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>4454</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>2006</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG86"/>
+  <dimension ref="A1:AG87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9343,6 +9343,109 @@
       </c>
       <c r="AG86" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1613</v>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1437550</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F87" t="n">
+        <v>12208</v>
+      </c>
+      <c r="G87" t="n">
+        <v>7</v>
+      </c>
+      <c r="H87" t="n">
+        <v>25011</v>
+      </c>
+      <c r="I87" t="n">
+        <v>11</v>
+      </c>
+      <c r="J87" t="n">
+        <v>46724</v>
+      </c>
+      <c r="K87" t="n">
+        <v>78</v>
+      </c>
+      <c r="L87" t="n">
+        <v>1968</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>1518</v>
+      </c>
+      <c r="O87" t="n">
+        <v>2</v>
+      </c>
+      <c r="P87" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>354</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>426836</v>
+      </c>
+      <c r="U87" t="n">
+        <v>1596</v>
+      </c>
+      <c r="V87" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>125358</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>571</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>4462</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG87"/>
+  <dimension ref="A1:AG88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9446,6 +9446,109 @@
       </c>
       <c r="AG87" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1614</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1438990</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F88" t="n">
+        <v>12217</v>
+      </c>
+      <c r="G88" t="n">
+        <v>9</v>
+      </c>
+      <c r="H88" t="n">
+        <v>25019</v>
+      </c>
+      <c r="I88" t="n">
+        <v>8</v>
+      </c>
+      <c r="J88" t="n">
+        <v>46794</v>
+      </c>
+      <c r="K88" t="n">
+        <v>70</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1969</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1518</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>354</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>426836</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>125811</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>453</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>4465</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>2031</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG88"/>
+  <dimension ref="A1:AG89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9549,6 +9549,109 @@
       </c>
       <c r="AG88" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1615</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1440580</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1590</v>
+      </c>
+      <c r="F89" t="n">
+        <v>12225</v>
+      </c>
+      <c r="G89" t="n">
+        <v>8</v>
+      </c>
+      <c r="H89" t="n">
+        <v>25032</v>
+      </c>
+      <c r="I89" t="n">
+        <v>13</v>
+      </c>
+      <c r="J89" t="n">
+        <v>46831</v>
+      </c>
+      <c r="K89" t="n">
+        <v>37</v>
+      </c>
+      <c r="L89" t="n">
+        <v>1969</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>1519</v>
+      </c>
+      <c r="O89" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>354</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>429555</v>
+      </c>
+      <c r="U89" t="n">
+        <v>2719</v>
+      </c>
+      <c r="V89" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>126302</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>491</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>4472</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>2038</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG89"/>
+  <dimension ref="A1:AG90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9652,6 +9652,109 @@
       </c>
       <c r="AG89" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1616</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1442140</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1560</v>
+      </c>
+      <c r="F90" t="n">
+        <v>12226</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>25038</v>
+      </c>
+      <c r="I90" t="n">
+        <v>6</v>
+      </c>
+      <c r="J90" t="n">
+        <v>46902</v>
+      </c>
+      <c r="K90" t="n">
+        <v>71</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1970</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>1519</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>354</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>431310</v>
+      </c>
+      <c r="U90" t="n">
+        <v>1755</v>
+      </c>
+      <c r="V90" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>126850</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>548</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>4476</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>2054</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG90"/>
+  <dimension ref="A1:AG91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9755,6 +9755,109 @@
       </c>
       <c r="AG90" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1617</v>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1443450</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F91" t="n">
+        <v>12227</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>25044</v>
+      </c>
+      <c r="I91" t="n">
+        <v>6</v>
+      </c>
+      <c r="J91" t="n">
+        <v>46962</v>
+      </c>
+      <c r="K91" t="n">
+        <v>60</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1973</v>
+      </c>
+      <c r="M91" t="n">
+        <v>3</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1521</v>
+      </c>
+      <c r="O91" t="n">
+        <v>2</v>
+      </c>
+      <c r="P91" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" t="n">
+        <v>354</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>432778</v>
+      </c>
+      <c r="U91" t="n">
+        <v>1468</v>
+      </c>
+      <c r="V91" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W91" t="n">
+        <v>0</v>
+      </c>
+      <c r="X91" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>127181</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>331</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>4478</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>2063</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG91"/>
+  <dimension ref="A1:AG92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9858,6 +9858,109 @@
       </c>
       <c r="AG91" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1618</v>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1444810</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F92" t="n">
+        <v>12230</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3</v>
+      </c>
+      <c r="H92" t="n">
+        <v>25049</v>
+      </c>
+      <c r="I92" t="n">
+        <v>5</v>
+      </c>
+      <c r="J92" t="n">
+        <v>47003</v>
+      </c>
+      <c r="K92" t="n">
+        <v>41</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1976</v>
+      </c>
+      <c r="M92" t="n">
+        <v>3</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1522</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="n">
+        <v>354</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>434140</v>
+      </c>
+      <c r="U92" t="n">
+        <v>1362</v>
+      </c>
+      <c r="V92" t="n">
+        <v>4909</v>
+      </c>
+      <c r="W92" t="n">
+        <v>0</v>
+      </c>
+      <c r="X92" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>127621</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>440</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>4480</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>2071</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG92"/>
+  <dimension ref="A1:AG93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9961,6 +9961,109 @@
       </c>
       <c r="AG92" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1619</v>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1446150</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1340</v>
+      </c>
+      <c r="F93" t="n">
+        <v>12231</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>25056</v>
+      </c>
+      <c r="I93" t="n">
+        <v>7</v>
+      </c>
+      <c r="J93" t="n">
+        <v>47045</v>
+      </c>
+      <c r="K93" t="n">
+        <v>42</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1976</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1525</v>
+      </c>
+      <c r="O93" t="n">
+        <v>3</v>
+      </c>
+      <c r="P93" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>354</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>435665</v>
+      </c>
+      <c r="U93" t="n">
+        <v>1525</v>
+      </c>
+      <c r="V93" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W93" t="n">
+        <v>0</v>
+      </c>
+      <c r="X93" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>128034</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>413</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>4483</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>2081</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG93"/>
+  <dimension ref="A1:AG94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10064,6 +10064,109 @@
       </c>
       <c r="AG93" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1620</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1447620</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F94" t="n">
+        <v>12231</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>25060</v>
+      </c>
+      <c r="I94" t="n">
+        <v>4</v>
+      </c>
+      <c r="J94" t="n">
+        <v>47127</v>
+      </c>
+      <c r="K94" t="n">
+        <v>82</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1980</v>
+      </c>
+      <c r="M94" t="n">
+        <v>4</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1527</v>
+      </c>
+      <c r="O94" t="n">
+        <v>2</v>
+      </c>
+      <c r="P94" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" t="n">
+        <v>354</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>437503</v>
+      </c>
+      <c r="U94" t="n">
+        <v>1838</v>
+      </c>
+      <c r="V94" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W94" t="n">
+        <v>0</v>
+      </c>
+      <c r="X94" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>128497</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>463</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>4484</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>2097</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG94"/>
+  <dimension ref="A1:AG95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10167,6 +10167,109 @@
       </c>
       <c r="AG94" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1621</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1449120</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F95" t="n">
+        <v>12231</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>25070</v>
+      </c>
+      <c r="I95" t="n">
+        <v>10</v>
+      </c>
+      <c r="J95" t="n">
+        <v>47196</v>
+      </c>
+      <c r="K95" t="n">
+        <v>69</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1988</v>
+      </c>
+      <c r="M95" t="n">
+        <v>8</v>
+      </c>
+      <c r="N95" t="n">
+        <v>1529</v>
+      </c>
+      <c r="O95" t="n">
+        <v>2</v>
+      </c>
+      <c r="P95" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="n">
+        <v>354</v>
+      </c>
+      <c r="S95" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" t="n">
+        <v>439291</v>
+      </c>
+      <c r="U95" t="n">
+        <v>1788</v>
+      </c>
+      <c r="V95" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W95" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>128953</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>456</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>4486</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>2108</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG95"/>
+  <dimension ref="A1:AG96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10270,6 +10270,109 @@
       </c>
       <c r="AG95" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1622</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1450510</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F96" t="n">
+        <v>12232</v>
+      </c>
+      <c r="G96" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>25075</v>
+      </c>
+      <c r="I96" t="n">
+        <v>5</v>
+      </c>
+      <c r="J96" t="n">
+        <v>47276</v>
+      </c>
+      <c r="K96" t="n">
+        <v>80</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1996</v>
+      </c>
+      <c r="M96" t="n">
+        <v>8</v>
+      </c>
+      <c r="N96" t="n">
+        <v>1533</v>
+      </c>
+      <c r="O96" t="n">
+        <v>4</v>
+      </c>
+      <c r="P96" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" t="n">
+        <v>354</v>
+      </c>
+      <c r="S96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
+        <v>440948</v>
+      </c>
+      <c r="U96" t="n">
+        <v>1657</v>
+      </c>
+      <c r="V96" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W96" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>129438</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>485</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>4492</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>2112</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG96"/>
+  <dimension ref="A1:AG97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10373,6 +10373,109 @@
       </c>
       <c r="AG96" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1623</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1451750</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F97" t="n">
+        <v>12237</v>
+      </c>
+      <c r="G97" t="n">
+        <v>5</v>
+      </c>
+      <c r="H97" t="n">
+        <v>25079</v>
+      </c>
+      <c r="I97" t="n">
+        <v>4</v>
+      </c>
+      <c r="J97" t="n">
+        <v>47331</v>
+      </c>
+      <c r="K97" t="n">
+        <v>55</v>
+      </c>
+      <c r="L97" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M97" t="n">
+        <v>4</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1538</v>
+      </c>
+      <c r="O97" t="n">
+        <v>5</v>
+      </c>
+      <c r="P97" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="n">
+        <v>354</v>
+      </c>
+      <c r="S97" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" t="n">
+        <v>442740</v>
+      </c>
+      <c r="U97" t="n">
+        <v>1792</v>
+      </c>
+      <c r="V97" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W97" t="n">
+        <v>0</v>
+      </c>
+      <c r="X97" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>129817</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>379</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>4492</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>2124</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG97"/>
+  <dimension ref="A1:AG98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10476,6 +10476,109 @@
       </c>
       <c r="AG97" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1624</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1452880</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1130</v>
+      </c>
+      <c r="F98" t="n">
+        <v>12242</v>
+      </c>
+      <c r="G98" t="n">
+        <v>5</v>
+      </c>
+      <c r="H98" t="n">
+        <v>25084</v>
+      </c>
+      <c r="I98" t="n">
+        <v>5</v>
+      </c>
+      <c r="J98" t="n">
+        <v>47396</v>
+      </c>
+      <c r="K98" t="n">
+        <v>65</v>
+      </c>
+      <c r="L98" t="n">
+        <v>2002</v>
+      </c>
+      <c r="M98" t="n">
+        <v>2</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1540</v>
+      </c>
+      <c r="O98" t="n">
+        <v>2</v>
+      </c>
+      <c r="P98" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="n">
+        <v>354</v>
+      </c>
+      <c r="S98" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" t="n">
+        <v>444455</v>
+      </c>
+      <c r="U98" t="n">
+        <v>1715</v>
+      </c>
+      <c r="V98" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W98" t="n">
+        <v>0</v>
+      </c>
+      <c r="X98" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>130266</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>449</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>4495</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>2134</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG98"/>
+  <dimension ref="A1:AG99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10579,6 +10579,109 @@
       </c>
       <c r="AG98" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1625</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1454210</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1330</v>
+      </c>
+      <c r="F99" t="n">
+        <v>12246</v>
+      </c>
+      <c r="G99" t="n">
+        <v>4</v>
+      </c>
+      <c r="H99" t="n">
+        <v>25087</v>
+      </c>
+      <c r="I99" t="n">
+        <v>3</v>
+      </c>
+      <c r="J99" t="n">
+        <v>47455</v>
+      </c>
+      <c r="K99" t="n">
+        <v>59</v>
+      </c>
+      <c r="L99" t="n">
+        <v>2006</v>
+      </c>
+      <c r="M99" t="n">
+        <v>4</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1547</v>
+      </c>
+      <c r="O99" t="n">
+        <v>7</v>
+      </c>
+      <c r="P99" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>354</v>
+      </c>
+      <c r="S99" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" t="n">
+        <v>446266</v>
+      </c>
+      <c r="U99" t="n">
+        <v>1811</v>
+      </c>
+      <c r="V99" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W99" t="n">
+        <v>0</v>
+      </c>
+      <c r="X99" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>130682</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>416</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>4496</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>2138</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG99"/>
+  <dimension ref="A1:AG100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10682,6 +10682,109 @@
       </c>
       <c r="AG99" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1626</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1455420</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1210</v>
+      </c>
+      <c r="F100" t="n">
+        <v>12247</v>
+      </c>
+      <c r="G100" t="n">
+        <v>1</v>
+      </c>
+      <c r="H100" t="n">
+        <v>25098</v>
+      </c>
+      <c r="I100" t="n">
+        <v>11</v>
+      </c>
+      <c r="J100" t="n">
+        <v>47522</v>
+      </c>
+      <c r="K100" t="n">
+        <v>67</v>
+      </c>
+      <c r="L100" t="n">
+        <v>2008</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2</v>
+      </c>
+      <c r="N100" t="n">
+        <v>1550</v>
+      </c>
+      <c r="O100" t="n">
+        <v>3</v>
+      </c>
+      <c r="P100" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>354</v>
+      </c>
+      <c r="S100" t="n">
+        <v>0</v>
+      </c>
+      <c r="T100" t="n">
+        <v>447855</v>
+      </c>
+      <c r="U100" t="n">
+        <v>1589</v>
+      </c>
+      <c r="V100" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W100" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>131068</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>386</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>4502</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>2152</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG100"/>
+  <dimension ref="A1:AG101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10785,6 +10785,109 @@
       </c>
       <c r="AG100" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1627</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>1456610</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F101" t="n">
+        <v>12251</v>
+      </c>
+      <c r="G101" t="n">
+        <v>4</v>
+      </c>
+      <c r="H101" t="n">
+        <v>25099</v>
+      </c>
+      <c r="I101" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" t="n">
+        <v>47580</v>
+      </c>
+      <c r="K101" t="n">
+        <v>58</v>
+      </c>
+      <c r="L101" t="n">
+        <v>2009</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1556</v>
+      </c>
+      <c r="O101" t="n">
+        <v>6</v>
+      </c>
+      <c r="P101" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>354</v>
+      </c>
+      <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>449606</v>
+      </c>
+      <c r="U101" t="n">
+        <v>1751</v>
+      </c>
+      <c r="V101" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W101" t="n">
+        <v>0</v>
+      </c>
+      <c r="X101" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>131417</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>349</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>4504</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>2162</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG101"/>
+  <dimension ref="A1:AG102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10888,6 +10888,109 @@
       </c>
       <c r="AG101" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1628</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1457740</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1130</v>
+      </c>
+      <c r="F102" t="n">
+        <v>12253</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" t="n">
+        <v>25103</v>
+      </c>
+      <c r="I102" t="n">
+        <v>4</v>
+      </c>
+      <c r="J102" t="n">
+        <v>47621</v>
+      </c>
+      <c r="K102" t="n">
+        <v>41</v>
+      </c>
+      <c r="L102" t="n">
+        <v>2013</v>
+      </c>
+      <c r="M102" t="n">
+        <v>4</v>
+      </c>
+      <c r="N102" t="n">
+        <v>1556</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" t="n">
+        <v>354</v>
+      </c>
+      <c r="S102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
+        <v>451248</v>
+      </c>
+      <c r="U102" t="n">
+        <v>1642</v>
+      </c>
+      <c r="V102" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W102" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>131775</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>358</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>4505</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>2171</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG102"/>
+  <dimension ref="A1:AG103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10991,6 +10991,109 @@
       </c>
       <c r="AG102" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1629</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1459210</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F103" t="n">
+        <v>12255</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>25116</v>
+      </c>
+      <c r="I103" t="n">
+        <v>13</v>
+      </c>
+      <c r="J103" t="n">
+        <v>47669</v>
+      </c>
+      <c r="K103" t="n">
+        <v>48</v>
+      </c>
+      <c r="L103" t="n">
+        <v>2019</v>
+      </c>
+      <c r="M103" t="n">
+        <v>6</v>
+      </c>
+      <c r="N103" t="n">
+        <v>1558</v>
+      </c>
+      <c r="O103" t="n">
+        <v>2</v>
+      </c>
+      <c r="P103" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="n">
+        <v>354</v>
+      </c>
+      <c r="S103" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" t="n">
+        <v>452994</v>
+      </c>
+      <c r="U103" t="n">
+        <v>1746</v>
+      </c>
+      <c r="V103" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W103" t="n">
+        <v>0</v>
+      </c>
+      <c r="X103" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>132236</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>461</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>4511</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>2181</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG103"/>
+  <dimension ref="A1:AG104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11094,6 +11094,109 @@
       </c>
       <c r="AG103" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1630</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>1460400</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F104" t="n">
+        <v>12259</v>
+      </c>
+      <c r="G104" t="n">
+        <v>4</v>
+      </c>
+      <c r="H104" t="n">
+        <v>25120</v>
+      </c>
+      <c r="I104" t="n">
+        <v>4</v>
+      </c>
+      <c r="J104" t="n">
+        <v>47713</v>
+      </c>
+      <c r="K104" t="n">
+        <v>44</v>
+      </c>
+      <c r="L104" t="n">
+        <v>2020</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1</v>
+      </c>
+      <c r="N104" t="n">
+        <v>1560</v>
+      </c>
+      <c r="O104" t="n">
+        <v>2</v>
+      </c>
+      <c r="P104" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="R104" t="n">
+        <v>354</v>
+      </c>
+      <c r="S104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
+        <v>454572</v>
+      </c>
+      <c r="U104" t="n">
+        <v>1578</v>
+      </c>
+      <c r="V104" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W104" t="n">
+        <v>0</v>
+      </c>
+      <c r="X104" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>132543</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>307</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>4514</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>2190</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG104"/>
+  <dimension ref="A1:AG105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11197,6 +11197,109 @@
       </c>
       <c r="AG104" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1631</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1461660</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F105" t="n">
+        <v>12259</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>25127</v>
+      </c>
+      <c r="I105" t="n">
+        <v>7</v>
+      </c>
+      <c r="J105" t="n">
+        <v>47773</v>
+      </c>
+      <c r="K105" t="n">
+        <v>60</v>
+      </c>
+      <c r="L105" t="n">
+        <v>2022</v>
+      </c>
+      <c r="M105" t="n">
+        <v>2</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1561</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="n">
+        <v>354</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0</v>
+      </c>
+      <c r="T105" t="n">
+        <v>456339</v>
+      </c>
+      <c r="U105" t="n">
+        <v>1767</v>
+      </c>
+      <c r="V105" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W105" t="n">
+        <v>0</v>
+      </c>
+      <c r="X105" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>132931</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>388</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>4516</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>2203</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG105"/>
+  <dimension ref="A1:AG106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11300,6 +11300,109 @@
       </c>
       <c r="AG105" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1632</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>1462970</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F106" t="n">
+        <v>12262</v>
+      </c>
+      <c r="G106" t="n">
+        <v>3</v>
+      </c>
+      <c r="H106" t="n">
+        <v>25130</v>
+      </c>
+      <c r="I106" t="n">
+        <v>3</v>
+      </c>
+      <c r="J106" t="n">
+        <v>47824</v>
+      </c>
+      <c r="K106" t="n">
+        <v>51</v>
+      </c>
+      <c r="L106" t="n">
+        <v>2023</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1</v>
+      </c>
+      <c r="N106" t="n">
+        <v>1562</v>
+      </c>
+      <c r="O106" t="n">
+        <v>1</v>
+      </c>
+      <c r="P106" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>354</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>457973</v>
+      </c>
+      <c r="U106" t="n">
+        <v>1634</v>
+      </c>
+      <c r="V106" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>133405</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>474</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>4522</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>2215</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG106"/>
+  <dimension ref="A1:AG107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11403,6 +11403,109 @@
       </c>
       <c r="AG106" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1633</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>1464440</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1470</v>
+      </c>
+      <c r="F107" t="n">
+        <v>12264</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" t="n">
+        <v>25141</v>
+      </c>
+      <c r="I107" t="n">
+        <v>11</v>
+      </c>
+      <c r="J107" t="n">
+        <v>47870</v>
+      </c>
+      <c r="K107" t="n">
+        <v>46</v>
+      </c>
+      <c r="L107" t="n">
+        <v>2024</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1</v>
+      </c>
+      <c r="N107" t="n">
+        <v>1565</v>
+      </c>
+      <c r="O107" t="n">
+        <v>3</v>
+      </c>
+      <c r="P107" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>354</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>459649</v>
+      </c>
+      <c r="U107" t="n">
+        <v>1676</v>
+      </c>
+      <c r="V107" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>133853</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>448</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>4524</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>2229</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG107"/>
+  <dimension ref="A1:AG108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11506,6 +11506,109 @@
       </c>
       <c r="AG107" t="n">
         <v>14</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1634</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>1465810</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1370</v>
+      </c>
+      <c r="F108" t="n">
+        <v>12269</v>
+      </c>
+      <c r="G108" t="n">
+        <v>5</v>
+      </c>
+      <c r="H108" t="n">
+        <v>25144</v>
+      </c>
+      <c r="I108" t="n">
+        <v>3</v>
+      </c>
+      <c r="J108" t="n">
+        <v>47932</v>
+      </c>
+      <c r="K108" t="n">
+        <v>62</v>
+      </c>
+      <c r="L108" t="n">
+        <v>2026</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>1568</v>
+      </c>
+      <c r="O108" t="n">
+        <v>3</v>
+      </c>
+      <c r="P108" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>354</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>461484</v>
+      </c>
+      <c r="U108" t="n">
+        <v>1835</v>
+      </c>
+      <c r="V108" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>134375</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>522</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>4528</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>2241</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG108"/>
+  <dimension ref="A1:AG109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11609,6 +11609,109 @@
       </c>
       <c r="AG108" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1635</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1467320</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1510</v>
+      </c>
+      <c r="F109" t="n">
+        <v>12270</v>
+      </c>
+      <c r="G109" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" t="n">
+        <v>25151</v>
+      </c>
+      <c r="I109" t="n">
+        <v>7</v>
+      </c>
+      <c r="J109" t="n">
+        <v>48007</v>
+      </c>
+      <c r="K109" t="n">
+        <v>75</v>
+      </c>
+      <c r="L109" t="n">
+        <v>2034</v>
+      </c>
+      <c r="M109" t="n">
+        <v>8</v>
+      </c>
+      <c r="N109" t="n">
+        <v>1570</v>
+      </c>
+      <c r="O109" t="n">
+        <v>2</v>
+      </c>
+      <c r="P109" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>354</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>463404</v>
+      </c>
+      <c r="U109" t="n">
+        <v>1920</v>
+      </c>
+      <c r="V109" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>134851</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>476</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>4535</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>2257</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG109"/>
+  <dimension ref="A1:AG110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11711,6 +11711,109 @@
         <v>2257</v>
       </c>
       <c r="AG109" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1636</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1468760</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F110" t="n">
+        <v>12272</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2</v>
+      </c>
+      <c r="H110" t="n">
+        <v>25155</v>
+      </c>
+      <c r="I110" t="n">
+        <v>4</v>
+      </c>
+      <c r="J110" t="n">
+        <v>48100</v>
+      </c>
+      <c r="K110" t="n">
+        <v>93</v>
+      </c>
+      <c r="L110" t="n">
+        <v>2037</v>
+      </c>
+      <c r="M110" t="n">
+        <v>3</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1572</v>
+      </c>
+      <c r="O110" t="n">
+        <v>2</v>
+      </c>
+      <c r="P110" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>354</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>465497</v>
+      </c>
+      <c r="U110" t="n">
+        <v>2093</v>
+      </c>
+      <c r="V110" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>135448</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>597</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>4540</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>2273</v>
+      </c>
+      <c r="AG110" t="n">
         <v>16</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG110"/>
+  <dimension ref="A1:AG111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11815,6 +11815,109 @@
       </c>
       <c r="AG110" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1637</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1469970</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1210</v>
+      </c>
+      <c r="F111" t="n">
+        <v>12274</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" t="n">
+        <v>25162</v>
+      </c>
+      <c r="I111" t="n">
+        <v>7</v>
+      </c>
+      <c r="J111" t="n">
+        <v>48155</v>
+      </c>
+      <c r="K111" t="n">
+        <v>55</v>
+      </c>
+      <c r="L111" t="n">
+        <v>2040</v>
+      </c>
+      <c r="M111" t="n">
+        <v>3</v>
+      </c>
+      <c r="N111" t="n">
+        <v>1577</v>
+      </c>
+      <c r="O111" t="n">
+        <v>5</v>
+      </c>
+      <c r="P111" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0</v>
+      </c>
+      <c r="R111" t="n">
+        <v>354</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>467459</v>
+      </c>
+      <c r="U111" t="n">
+        <v>1962</v>
+      </c>
+      <c r="V111" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>135891</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>443</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>4547</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>2292</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG111"/>
+  <dimension ref="A1:AG112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11917,6 +11917,109 @@
         <v>2292</v>
       </c>
       <c r="AG111" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1638</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1471160</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F112" t="n">
+        <v>12276</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" t="n">
+        <v>25162</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>48205</v>
+      </c>
+      <c r="K112" t="n">
+        <v>50</v>
+      </c>
+      <c r="L112" t="n">
+        <v>2043</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3</v>
+      </c>
+      <c r="N112" t="n">
+        <v>1577</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="R112" t="n">
+        <v>354</v>
+      </c>
+      <c r="S112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
+        <v>469197</v>
+      </c>
+      <c r="U112" t="n">
+        <v>1738</v>
+      </c>
+      <c r="V112" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W112" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>136318</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>427</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>4548</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AG112" t="n">
         <v>19</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG112"/>
+  <dimension ref="A1:AG113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12021,6 +12021,109 @@
       </c>
       <c r="AG112" t="n">
         <v>19</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1639</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1472640</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F113" t="n">
+        <v>12283</v>
+      </c>
+      <c r="G113" t="n">
+        <v>7</v>
+      </c>
+      <c r="H113" t="n">
+        <v>25165</v>
+      </c>
+      <c r="I113" t="n">
+        <v>3</v>
+      </c>
+      <c r="J113" t="n">
+        <v>48261</v>
+      </c>
+      <c r="K113" t="n">
+        <v>56</v>
+      </c>
+      <c r="L113" t="n">
+        <v>2050</v>
+      </c>
+      <c r="M113" t="n">
+        <v>7</v>
+      </c>
+      <c r="N113" t="n">
+        <v>1577</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0</v>
+      </c>
+      <c r="R113" t="n">
+        <v>354</v>
+      </c>
+      <c r="S113" t="n">
+        <v>0</v>
+      </c>
+      <c r="T113" t="n">
+        <v>470869</v>
+      </c>
+      <c r="U113" t="n">
+        <v>1672</v>
+      </c>
+      <c r="V113" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W113" t="n">
+        <v>0</v>
+      </c>
+      <c r="X113" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>136818</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>500</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>4551</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>2321</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG113"/>
+  <dimension ref="A1:AG114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12124,6 +12124,109 @@
       </c>
       <c r="AG113" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1640</v>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1474030</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F114" t="n">
+        <v>12286</v>
+      </c>
+      <c r="G114" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" t="n">
+        <v>25170</v>
+      </c>
+      <c r="I114" t="n">
+        <v>5</v>
+      </c>
+      <c r="J114" t="n">
+        <v>48318</v>
+      </c>
+      <c r="K114" t="n">
+        <v>57</v>
+      </c>
+      <c r="L114" t="n">
+        <v>2052</v>
+      </c>
+      <c r="M114" t="n">
+        <v>2</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1581</v>
+      </c>
+      <c r="O114" t="n">
+        <v>4</v>
+      </c>
+      <c r="P114" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="n">
+        <v>354</v>
+      </c>
+      <c r="S114" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" t="n">
+        <v>472849</v>
+      </c>
+      <c r="U114" t="n">
+        <v>1980</v>
+      </c>
+      <c r="V114" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W114" t="n">
+        <v>0</v>
+      </c>
+      <c r="X114" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>137369</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>551</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>4559</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>2333</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG114"/>
+  <dimension ref="A1:AG115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12227,6 +12227,109 @@
       </c>
       <c r="AG114" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1641</v>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>1475270</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F115" t="n">
+        <v>12292</v>
+      </c>
+      <c r="G115" t="n">
+        <v>6</v>
+      </c>
+      <c r="H115" t="n">
+        <v>25176</v>
+      </c>
+      <c r="I115" t="n">
+        <v>6</v>
+      </c>
+      <c r="J115" t="n">
+        <v>48382</v>
+      </c>
+      <c r="K115" t="n">
+        <v>64</v>
+      </c>
+      <c r="L115" t="n">
+        <v>2054</v>
+      </c>
+      <c r="M115" t="n">
+        <v>2</v>
+      </c>
+      <c r="N115" t="n">
+        <v>1584</v>
+      </c>
+      <c r="O115" t="n">
+        <v>3</v>
+      </c>
+      <c r="P115" t="n">
+        <v>439</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="n">
+        <v>354</v>
+      </c>
+      <c r="S115" t="n">
+        <v>0</v>
+      </c>
+      <c r="T115" t="n">
+        <v>474641</v>
+      </c>
+      <c r="U115" t="n">
+        <v>1792</v>
+      </c>
+      <c r="V115" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W115" t="n">
+        <v>0</v>
+      </c>
+      <c r="X115" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>137804</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>435</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>4565</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>2344</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG115"/>
+  <dimension ref="A1:AG116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12330,6 +12330,109 @@
       </c>
       <c r="AG115" t="n">
         <v>11</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1642</v>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1476580</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1310</v>
+      </c>
+      <c r="F116" t="n">
+        <v>12292</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>25202</v>
+      </c>
+      <c r="I116" t="n">
+        <v>26</v>
+      </c>
+      <c r="J116" t="n">
+        <v>48451</v>
+      </c>
+      <c r="K116" t="n">
+        <v>69</v>
+      </c>
+      <c r="L116" t="n">
+        <v>2054</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1585</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1</v>
+      </c>
+      <c r="P116" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>1</v>
+      </c>
+      <c r="R116" t="n">
+        <v>354</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>476566</v>
+      </c>
+      <c r="U116" t="n">
+        <v>1925</v>
+      </c>
+      <c r="V116" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>138219</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>415</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>4569</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>2352</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG116"/>
+  <dimension ref="A1:AG117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12433,6 +12433,109 @@
       </c>
       <c r="AG116" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1643</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1478070</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F117" t="n">
+        <v>12293</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>25211</v>
+      </c>
+      <c r="I117" t="n">
+        <v>9</v>
+      </c>
+      <c r="J117" t="n">
+        <v>48519</v>
+      </c>
+      <c r="K117" t="n">
+        <v>68</v>
+      </c>
+      <c r="L117" t="n">
+        <v>2056</v>
+      </c>
+      <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>1586</v>
+      </c>
+      <c r="O117" t="n">
+        <v>1</v>
+      </c>
+      <c r="P117" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0</v>
+      </c>
+      <c r="R117" t="n">
+        <v>354</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0</v>
+      </c>
+      <c r="T117" t="n">
+        <v>478327</v>
+      </c>
+      <c r="U117" t="n">
+        <v>1761</v>
+      </c>
+      <c r="V117" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>138773</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>554</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>4575</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>2368</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG117"/>
+  <dimension ref="A1:AG118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12536,6 +12536,109 @@
       </c>
       <c r="AG117" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1644</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1479300</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F118" t="n">
+        <v>12293</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>25220</v>
+      </c>
+      <c r="I118" t="n">
+        <v>9</v>
+      </c>
+      <c r="J118" t="n">
+        <v>48567</v>
+      </c>
+      <c r="K118" t="n">
+        <v>48</v>
+      </c>
+      <c r="L118" t="n">
+        <v>2058</v>
+      </c>
+      <c r="M118" t="n">
+        <v>2</v>
+      </c>
+      <c r="N118" t="n">
+        <v>1587</v>
+      </c>
+      <c r="O118" t="n">
+        <v>1</v>
+      </c>
+      <c r="P118" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0</v>
+      </c>
+      <c r="R118" t="n">
+        <v>354</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0</v>
+      </c>
+      <c r="T118" t="n">
+        <v>479882</v>
+      </c>
+      <c r="U118" t="n">
+        <v>1555</v>
+      </c>
+      <c r="V118" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0</v>
+      </c>
+      <c r="X118" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>139221</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>448</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>4582</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>2378</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG118"/>
+  <dimension ref="A1:AG119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12639,6 +12639,109 @@
       </c>
       <c r="AG118" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1645</v>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1480750</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1450</v>
+      </c>
+      <c r="F119" t="n">
+        <v>12300</v>
+      </c>
+      <c r="G119" t="n">
+        <v>7</v>
+      </c>
+      <c r="H119" t="n">
+        <v>25230</v>
+      </c>
+      <c r="I119" t="n">
+        <v>10</v>
+      </c>
+      <c r="J119" t="n">
+        <v>48641</v>
+      </c>
+      <c r="K119" t="n">
+        <v>74</v>
+      </c>
+      <c r="L119" t="n">
+        <v>2062</v>
+      </c>
+      <c r="M119" t="n">
+        <v>4</v>
+      </c>
+      <c r="N119" t="n">
+        <v>1588</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1</v>
+      </c>
+      <c r="P119" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0</v>
+      </c>
+      <c r="R119" t="n">
+        <v>354</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0</v>
+      </c>
+      <c r="T119" t="n">
+        <v>481605</v>
+      </c>
+      <c r="U119" t="n">
+        <v>1723</v>
+      </c>
+      <c r="V119" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0</v>
+      </c>
+      <c r="X119" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>139754</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>533</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>4592</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>2387</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG119"/>
+  <dimension ref="A1:AG120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12742,6 +12742,109 @@
       </c>
       <c r="AG119" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1646</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1482150</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F120" t="n">
+        <v>12304</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4</v>
+      </c>
+      <c r="H120" t="n">
+        <v>25237</v>
+      </c>
+      <c r="I120" t="n">
+        <v>7</v>
+      </c>
+      <c r="J120" t="n">
+        <v>48694</v>
+      </c>
+      <c r="K120" t="n">
+        <v>53</v>
+      </c>
+      <c r="L120" t="n">
+        <v>2065</v>
+      </c>
+      <c r="M120" t="n">
+        <v>3</v>
+      </c>
+      <c r="N120" t="n">
+        <v>1590</v>
+      </c>
+      <c r="O120" t="n">
+        <v>2</v>
+      </c>
+      <c r="P120" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" t="n">
+        <v>354</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
+        <v>483367</v>
+      </c>
+      <c r="U120" t="n">
+        <v>1762</v>
+      </c>
+      <c r="V120" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>140248</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>494</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>4602</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>2404</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG120"/>
+  <dimension ref="A1:AG121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12845,6 +12845,109 @@
       </c>
       <c r="AG120" t="n">
         <v>17</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1647</v>
+      </c>
+      <c r="C121" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1483780</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1630</v>
+      </c>
+      <c r="F121" t="n">
+        <v>12307</v>
+      </c>
+      <c r="G121" t="n">
+        <v>3</v>
+      </c>
+      <c r="H121" t="n">
+        <v>25237</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>48749</v>
+      </c>
+      <c r="K121" t="n">
+        <v>55</v>
+      </c>
+      <c r="L121" t="n">
+        <v>2067</v>
+      </c>
+      <c r="M121" t="n">
+        <v>2</v>
+      </c>
+      <c r="N121" t="n">
+        <v>1593</v>
+      </c>
+      <c r="O121" t="n">
+        <v>3</v>
+      </c>
+      <c r="P121" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>354</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" t="n">
+        <v>485024</v>
+      </c>
+      <c r="U121" t="n">
+        <v>1657</v>
+      </c>
+      <c r="V121" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>140741</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>493</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>4604</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>2420</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG121"/>
+  <dimension ref="A1:AG122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12948,6 +12948,109 @@
       </c>
       <c r="AG121" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1648</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1485200</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1420</v>
+      </c>
+      <c r="F122" t="n">
+        <v>12310</v>
+      </c>
+      <c r="G122" t="n">
+        <v>3</v>
+      </c>
+      <c r="H122" t="n">
+        <v>25241</v>
+      </c>
+      <c r="I122" t="n">
+        <v>4</v>
+      </c>
+      <c r="J122" t="n">
+        <v>48774</v>
+      </c>
+      <c r="K122" t="n">
+        <v>25</v>
+      </c>
+      <c r="L122" t="n">
+        <v>2070</v>
+      </c>
+      <c r="M122" t="n">
+        <v>3</v>
+      </c>
+      <c r="N122" t="n">
+        <v>1593</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="P122" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0</v>
+      </c>
+      <c r="R122" t="n">
+        <v>354</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0</v>
+      </c>
+      <c r="T122" t="n">
+        <v>486384</v>
+      </c>
+      <c r="U122" t="n">
+        <v>1360</v>
+      </c>
+      <c r="V122" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>141059</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>318</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>4608</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>2429</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG122"/>
+  <dimension ref="A1:AG123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13051,6 +13051,109 @@
       </c>
       <c r="AG122" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1649</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1486600</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F123" t="n">
+        <v>12311</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>25248</v>
+      </c>
+      <c r="I123" t="n">
+        <v>7</v>
+      </c>
+      <c r="J123" t="n">
+        <v>48833</v>
+      </c>
+      <c r="K123" t="n">
+        <v>59</v>
+      </c>
+      <c r="L123" t="n">
+        <v>2072</v>
+      </c>
+      <c r="M123" t="n">
+        <v>2</v>
+      </c>
+      <c r="N123" t="n">
+        <v>1594</v>
+      </c>
+      <c r="O123" t="n">
+        <v>1</v>
+      </c>
+      <c r="P123" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>354</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0</v>
+      </c>
+      <c r="T123" t="n">
+        <v>488347</v>
+      </c>
+      <c r="U123" t="n">
+        <v>1963</v>
+      </c>
+      <c r="V123" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>141453</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>394</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>4614</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>2435</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG123"/>
+  <dimension ref="A1:AG124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13154,6 +13154,109 @@
       </c>
       <c r="AG123" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1488200</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F124" t="n">
+        <v>12316</v>
+      </c>
+      <c r="G124" t="n">
+        <v>5</v>
+      </c>
+      <c r="H124" t="n">
+        <v>25255</v>
+      </c>
+      <c r="I124" t="n">
+        <v>7</v>
+      </c>
+      <c r="J124" t="n">
+        <v>48883</v>
+      </c>
+      <c r="K124" t="n">
+        <v>50</v>
+      </c>
+      <c r="L124" t="n">
+        <v>2079</v>
+      </c>
+      <c r="M124" t="n">
+        <v>7</v>
+      </c>
+      <c r="N124" t="n">
+        <v>1597</v>
+      </c>
+      <c r="O124" t="n">
+        <v>3</v>
+      </c>
+      <c r="P124" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>354</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0</v>
+      </c>
+      <c r="T124" t="n">
+        <v>490402</v>
+      </c>
+      <c r="U124" t="n">
+        <v>2055</v>
+      </c>
+      <c r="V124" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0</v>
+      </c>
+      <c r="X124" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>141920</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>467</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>4621</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>2442</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG124"/>
+  <dimension ref="A1:AG125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13257,6 +13257,109 @@
       </c>
       <c r="AG124" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1651</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>1489640</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F125" t="n">
+        <v>12320</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4</v>
+      </c>
+      <c r="H125" t="n">
+        <v>25257</v>
+      </c>
+      <c r="I125" t="n">
+        <v>2</v>
+      </c>
+      <c r="J125" t="n">
+        <v>48954</v>
+      </c>
+      <c r="K125" t="n">
+        <v>71</v>
+      </c>
+      <c r="L125" t="n">
+        <v>2079</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>1597</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>354</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0</v>
+      </c>
+      <c r="T125" t="n">
+        <v>492177</v>
+      </c>
+      <c r="U125" t="n">
+        <v>1775</v>
+      </c>
+      <c r="V125" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0</v>
+      </c>
+      <c r="X125" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>142332</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>412</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>4623</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>2452</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG125"/>
+  <dimension ref="A1:AG126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13360,6 +13360,109 @@
       </c>
       <c r="AG125" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1652</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1491030</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F126" t="n">
+        <v>12324</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4</v>
+      </c>
+      <c r="H126" t="n">
+        <v>25263</v>
+      </c>
+      <c r="I126" t="n">
+        <v>6</v>
+      </c>
+      <c r="J126" t="n">
+        <v>49016</v>
+      </c>
+      <c r="K126" t="n">
+        <v>62</v>
+      </c>
+      <c r="L126" t="n">
+        <v>2081</v>
+      </c>
+      <c r="M126" t="n">
+        <v>2</v>
+      </c>
+      <c r="N126" t="n">
+        <v>1598</v>
+      </c>
+      <c r="O126" t="n">
+        <v>1</v>
+      </c>
+      <c r="P126" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>354</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0</v>
+      </c>
+      <c r="T126" t="n">
+        <v>494146</v>
+      </c>
+      <c r="U126" t="n">
+        <v>1969</v>
+      </c>
+      <c r="V126" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>142715</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>383</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>4625</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>2464</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG126"/>
+  <dimension ref="A1:AG127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13462,6 +13462,109 @@
         <v>2464</v>
       </c>
       <c r="AG126" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1653</v>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1492350</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1320</v>
+      </c>
+      <c r="F127" t="n">
+        <v>12324</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>25264</v>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" t="n">
+        <v>49085</v>
+      </c>
+      <c r="K127" t="n">
+        <v>69</v>
+      </c>
+      <c r="L127" t="n">
+        <v>2085</v>
+      </c>
+      <c r="M127" t="n">
+        <v>4</v>
+      </c>
+      <c r="N127" t="n">
+        <v>1600</v>
+      </c>
+      <c r="O127" t="n">
+        <v>2</v>
+      </c>
+      <c r="P127" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>1</v>
+      </c>
+      <c r="R127" t="n">
+        <v>355</v>
+      </c>
+      <c r="S127" t="n">
+        <v>1</v>
+      </c>
+      <c r="T127" t="n">
+        <v>496021</v>
+      </c>
+      <c r="U127" t="n">
+        <v>1875</v>
+      </c>
+      <c r="V127" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>143150</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>435</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>4628</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>2476</v>
+      </c>
+      <c r="AG127" t="n">
         <v>12</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG127"/>
+  <dimension ref="A1:AG128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13566,6 +13566,109 @@
       </c>
       <c r="AG127" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1654</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>1493790</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F128" t="n">
+        <v>12325</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>25272</v>
+      </c>
+      <c r="I128" t="n">
+        <v>8</v>
+      </c>
+      <c r="J128" t="n">
+        <v>49162</v>
+      </c>
+      <c r="K128" t="n">
+        <v>77</v>
+      </c>
+      <c r="L128" t="n">
+        <v>2088</v>
+      </c>
+      <c r="M128" t="n">
+        <v>3</v>
+      </c>
+      <c r="N128" t="n">
+        <v>1604</v>
+      </c>
+      <c r="O128" t="n">
+        <v>4</v>
+      </c>
+      <c r="P128" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>355</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>497911</v>
+      </c>
+      <c r="U128" t="n">
+        <v>1890</v>
+      </c>
+      <c r="V128" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>143642</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>492</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>4636</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>2489</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG128"/>
+  <dimension ref="A1:AG129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13668,6 +13668,109 @@
         <v>2489</v>
       </c>
       <c r="AG128" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1655</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1495050</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1260</v>
+      </c>
+      <c r="F129" t="n">
+        <v>12328</v>
+      </c>
+      <c r="G129" t="n">
+        <v>3</v>
+      </c>
+      <c r="H129" t="n">
+        <v>25273</v>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" t="n">
+        <v>49227</v>
+      </c>
+      <c r="K129" t="n">
+        <v>65</v>
+      </c>
+      <c r="L129" t="n">
+        <v>2093</v>
+      </c>
+      <c r="M129" t="n">
+        <v>5</v>
+      </c>
+      <c r="N129" t="n">
+        <v>1604</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>355</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>499809</v>
+      </c>
+      <c r="U129" t="n">
+        <v>1898</v>
+      </c>
+      <c r="V129" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>144043</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>401</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>4644</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>2502</v>
+      </c>
+      <c r="AG129" t="n">
         <v>13</v>
       </c>
     </row>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG129"/>
+  <dimension ref="A1:AG130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13772,6 +13772,109 @@
       </c>
       <c r="AG129" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1656</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1496440</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F130" t="n">
+        <v>12331</v>
+      </c>
+      <c r="G130" t="n">
+        <v>3</v>
+      </c>
+      <c r="H130" t="n">
+        <v>25278</v>
+      </c>
+      <c r="I130" t="n">
+        <v>5</v>
+      </c>
+      <c r="J130" t="n">
+        <v>49260</v>
+      </c>
+      <c r="K130" t="n">
+        <v>33</v>
+      </c>
+      <c r="L130" t="n">
+        <v>2096</v>
+      </c>
+      <c r="M130" t="n">
+        <v>3</v>
+      </c>
+      <c r="N130" t="n">
+        <v>1605</v>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>355</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>501244</v>
+      </c>
+      <c r="U130" t="n">
+        <v>1435</v>
+      </c>
+      <c r="V130" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>144435</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>392</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>4644</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>2507</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG130"/>
+  <dimension ref="A1:AG131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13875,6 +13875,109 @@
       </c>
       <c r="AG130" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1657</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1497980</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1540</v>
+      </c>
+      <c r="F131" t="n">
+        <v>12332</v>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>25284</v>
+      </c>
+      <c r="I131" t="n">
+        <v>6</v>
+      </c>
+      <c r="J131" t="n">
+        <v>49311</v>
+      </c>
+      <c r="K131" t="n">
+        <v>51</v>
+      </c>
+      <c r="L131" t="n">
+        <v>2103</v>
+      </c>
+      <c r="M131" t="n">
+        <v>7</v>
+      </c>
+      <c r="N131" t="n">
+        <v>1609</v>
+      </c>
+      <c r="O131" t="n">
+        <v>4</v>
+      </c>
+      <c r="P131" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>355</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>502717</v>
+      </c>
+      <c r="U131" t="n">
+        <v>1473</v>
+      </c>
+      <c r="V131" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>145026</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>591</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>4647</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>2516</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG131"/>
+  <dimension ref="A1:AG132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13978,6 +13978,109 @@
       </c>
       <c r="AG131" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1658</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1499390</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1410</v>
+      </c>
+      <c r="F132" t="n">
+        <v>12332</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>25285</v>
+      </c>
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>49341</v>
+      </c>
+      <c r="K132" t="n">
+        <v>30</v>
+      </c>
+      <c r="L132" t="n">
+        <v>2104</v>
+      </c>
+      <c r="M132" t="n">
+        <v>1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>1612</v>
+      </c>
+      <c r="O132" t="n">
+        <v>3</v>
+      </c>
+      <c r="P132" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>355</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>504309</v>
+      </c>
+      <c r="U132" t="n">
+        <v>1592</v>
+      </c>
+      <c r="V132" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>145478</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>452</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>4647</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>2521</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG132"/>
+  <dimension ref="A1:AG133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14081,6 +14081,109 @@
       </c>
       <c r="AG132" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>1659</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1500870</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1480</v>
+      </c>
+      <c r="F133" t="n">
+        <v>12338</v>
+      </c>
+      <c r="G133" t="n">
+        <v>6</v>
+      </c>
+      <c r="H133" t="n">
+        <v>25290</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>49383</v>
+      </c>
+      <c r="K133" t="n">
+        <v>42</v>
+      </c>
+      <c r="L133" t="n">
+        <v>2105</v>
+      </c>
+      <c r="M133" t="n">
+        <v>1</v>
+      </c>
+      <c r="N133" t="n">
+        <v>1613</v>
+      </c>
+      <c r="O133" t="n">
+        <v>1</v>
+      </c>
+      <c r="P133" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>355</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>506188</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1879</v>
+      </c>
+      <c r="V133" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>146008</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>530</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>4650</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>2534</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG133"/>
+  <dimension ref="A1:AG134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14184,6 +14184,109 @@
       </c>
       <c r="AG133" t="n">
         <v>13</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>1660</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1502390</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F134" t="n">
+        <v>12339</v>
+      </c>
+      <c r="G134" t="n">
+        <v>1</v>
+      </c>
+      <c r="H134" t="n">
+        <v>25305</v>
+      </c>
+      <c r="I134" t="n">
+        <v>15</v>
+      </c>
+      <c r="J134" t="n">
+        <v>49452</v>
+      </c>
+      <c r="K134" t="n">
+        <v>69</v>
+      </c>
+      <c r="L134" t="n">
+        <v>2107</v>
+      </c>
+      <c r="M134" t="n">
+        <v>2</v>
+      </c>
+      <c r="N134" t="n">
+        <v>1618</v>
+      </c>
+      <c r="O134" t="n">
+        <v>5</v>
+      </c>
+      <c r="P134" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>356</v>
+      </c>
+      <c r="S134" t="n">
+        <v>1</v>
+      </c>
+      <c r="T134" t="n">
+        <v>508205</v>
+      </c>
+      <c r="U134" t="n">
+        <v>2017</v>
+      </c>
+      <c r="V134" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>146621</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>613</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>4650</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>2550</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG134"/>
+  <dimension ref="A1:AG135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14287,6 +14287,109 @@
       </c>
       <c r="AG134" t="n">
         <v>16</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1661</v>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1503880</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F135" t="n">
+        <v>12341</v>
+      </c>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>25312</v>
+      </c>
+      <c r="I135" t="n">
+        <v>7</v>
+      </c>
+      <c r="J135" t="n">
+        <v>49516</v>
+      </c>
+      <c r="K135" t="n">
+        <v>64</v>
+      </c>
+      <c r="L135" t="n">
+        <v>2109</v>
+      </c>
+      <c r="M135" t="n">
+        <v>2</v>
+      </c>
+      <c r="N135" t="n">
+        <v>1622</v>
+      </c>
+      <c r="O135" t="n">
+        <v>4</v>
+      </c>
+      <c r="P135" t="n">
+        <v>441</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>356</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>510130</v>
+      </c>
+      <c r="U135" t="n">
+        <v>1925</v>
+      </c>
+      <c r="V135" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>147211</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>590</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>4666</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>2573</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/mod_losses.xlsx
+++ b/data/mod_losses.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG135"/>
+  <dimension ref="A1:AG136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14390,6 +14390,109 @@
       </c>
       <c r="AG135" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1662</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>1505380</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F136" t="n">
+        <v>12342</v>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="n">
+        <v>25322</v>
+      </c>
+      <c r="I136" t="n">
+        <v>10</v>
+      </c>
+      <c r="J136" t="n">
+        <v>49601</v>
+      </c>
+      <c r="K136" t="n">
+        <v>85</v>
+      </c>
+      <c r="L136" t="n">
+        <v>2115</v>
+      </c>
+      <c r="M136" t="n">
+        <v>6</v>
+      </c>
+      <c r="N136" t="n">
+        <v>1633</v>
+      </c>
+      <c r="O136" t="n">
+        <v>11</v>
+      </c>
+      <c r="P136" t="n">
+        <v>442</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>1</v>
+      </c>
+      <c r="R136" t="n">
+        <v>356</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>512175</v>
+      </c>
+      <c r="U136" t="n">
+        <v>2045</v>
+      </c>
+      <c r="V136" t="n">
+        <v>4950</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>35</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>147849</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>638</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>4676</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>2586</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
